--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -8351,16 +8351,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.6309</v>
+        <v>22.5431</v>
       </c>
       <c r="J2" t="n">
-        <v>48593.91</v>
+        <v>48405.38</v>
       </c>
       <c r="K2" t="n">
-        <v>15.71</v>
+        <v>15.26</v>
       </c>
       <c r="L2" t="n">
-        <v>9.98</v>
+        <v>9.68</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -8406,16 +8406,16 @@
         <v>41997.9</v>
       </c>
       <c r="I3" t="n">
-        <v>12.5355</v>
+        <v>12.5017</v>
       </c>
       <c r="J3" t="n">
-        <v>54600.01</v>
+        <v>54452.79</v>
       </c>
       <c r="K3" t="n">
-        <v>30.01</v>
+        <v>29.66</v>
       </c>
       <c r="L3" t="n">
-        <v>18.32</v>
+        <v>18.08</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -8461,16 +8461,16 @@
         <v>39998</v>
       </c>
       <c r="I4" t="n">
-        <v>154.523</v>
+        <v>155.074</v>
       </c>
       <c r="J4" t="n">
-        <v>45995.32</v>
+        <v>46159.33</v>
       </c>
       <c r="K4" t="n">
-        <v>14.99</v>
+        <v>15.4</v>
       </c>
       <c r="L4" t="n">
-        <v>5.97</v>
+        <v>6.12</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -8516,16 +8516,16 @@
         <v>41997.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4975.989</v>
+        <v>4955.5286</v>
       </c>
       <c r="J5" t="n">
-        <v>49595.68</v>
+        <v>49391.75</v>
       </c>
       <c r="K5" t="n">
-        <v>18.09</v>
+        <v>17.61</v>
       </c>
       <c r="L5" t="n">
-        <v>11.58</v>
+        <v>11.26</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8571,16 +8571,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>46.7087</v>
+        <v>46.5163</v>
       </c>
       <c r="J6" t="n">
-        <v>47662.49</v>
+        <v>47466.16</v>
       </c>
       <c r="K6" t="n">
-        <v>13.49</v>
+        <v>13.02</v>
       </c>
       <c r="L6" t="n">
-        <v>8.529999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8626,16 +8626,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>16.7853</v>
+        <v>16.9349</v>
       </c>
       <c r="J7" t="n">
-        <v>47044.4</v>
+        <v>47463.68</v>
       </c>
       <c r="K7" t="n">
-        <v>12.02</v>
+        <v>13.01</v>
       </c>
       <c r="L7" t="n">
-        <v>7.78</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8681,16 +8681,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>168.616</v>
+        <v>169.225</v>
       </c>
       <c r="J8" t="n">
-        <v>43529.57</v>
+        <v>43686.79</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>4.02</v>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8736,16 +8736,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>11.747</v>
+        <v>11.748</v>
       </c>
       <c r="J9" t="n">
-        <v>47847.67</v>
+        <v>47851.74</v>
       </c>
       <c r="K9" t="n">
-        <v>13.93</v>
+        <v>13.94</v>
       </c>
       <c r="L9" t="n">
-        <v>8.76</v>
+        <v>8.75</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8791,16 +8791,16 @@
         <v>41997.9</v>
       </c>
       <c r="I10" t="n">
-        <v>27.8205</v>
+        <v>27.732</v>
       </c>
       <c r="J10" t="n">
-        <v>48767.42</v>
+        <v>48612.28</v>
       </c>
       <c r="K10" t="n">
-        <v>16.12</v>
+        <v>15.75</v>
       </c>
       <c r="L10" t="n">
-        <v>9.99</v>
+        <v>9.75</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10921,7 +10921,7 @@
         <v>15.26</v>
       </c>
       <c r="L2" t="n">
-        <v>9.68</v>
+        <v>9.66</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>29.66</v>
       </c>
       <c r="L4" t="n">
-        <v>18.08</v>
+        <v>18.05</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>17.61</v>
       </c>
       <c r="L6" t="n">
-        <v>11.26</v>
+        <v>11.24</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>13.02</v>
       </c>
       <c r="L7" t="n">
-        <v>8.23</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>13.01</v>
       </c>
       <c r="L8" t="n">
-        <v>8.390000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>13.94</v>
       </c>
       <c r="L11" t="n">
-        <v>8.75</v>
+        <v>8.73</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>15.75</v>
       </c>
       <c r="L12" t="n">
-        <v>9.75</v>
+        <v>9.73</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10921,7 +10921,7 @@
         <v>15.26</v>
       </c>
       <c r="L2" t="n">
-        <v>9.66</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>29.66</v>
       </c>
       <c r="L4" t="n">
-        <v>18.05</v>
+        <v>18.02</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>15.4</v>
       </c>
       <c r="L5" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>17.61</v>
       </c>
       <c r="L6" t="n">
-        <v>11.24</v>
+        <v>11.22</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>13.02</v>
       </c>
       <c r="L7" t="n">
-        <v>8.210000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>13.01</v>
       </c>
       <c r="L8" t="n">
-        <v>8.380000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>4.02</v>
       </c>
       <c r="L9" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>13.94</v>
       </c>
       <c r="L11" t="n">
-        <v>8.73</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>15.75</v>
       </c>
       <c r="L12" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.5431</v>
+        <v>22.6211</v>
       </c>
       <c r="J2" t="n">
-        <v>48405.38</v>
+        <v>48572.86</v>
       </c>
       <c r="K2" t="n">
-        <v>15.26</v>
+        <v>15.66</v>
       </c>
       <c r="L2" t="n">
-        <v>9.640000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>461.408</v>
+        <v>464.303</v>
       </c>
       <c r="J3" t="n">
-        <v>79392.17</v>
+        <v>79890.3</v>
       </c>
       <c r="K3" t="n">
-        <v>164.64</v>
+        <v>166.3</v>
       </c>
       <c r="L3" t="n">
-        <v>13.92</v>
+        <v>13.93</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5017</v>
+        <v>12.5571</v>
       </c>
       <c r="J4" t="n">
-        <v>54452.79</v>
+        <v>54694.09</v>
       </c>
       <c r="K4" t="n">
-        <v>29.66</v>
+        <v>30.23</v>
       </c>
       <c r="L4" t="n">
-        <v>18.02</v>
+        <v>18.31</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>155.074</v>
+        <v>155.78</v>
       </c>
       <c r="J5" t="n">
-        <v>46159.33</v>
+        <v>46369.47</v>
       </c>
       <c r="K5" t="n">
-        <v>15.4</v>
+        <v>15.93</v>
       </c>
       <c r="L5" t="n">
-        <v>6.11</v>
+        <v>6.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4955.5286</v>
+        <v>4966.8626</v>
       </c>
       <c r="J6" t="n">
-        <v>49391.75</v>
+        <v>49504.72</v>
       </c>
       <c r="K6" t="n">
-        <v>17.61</v>
+        <v>17.87</v>
       </c>
       <c r="L6" t="n">
-        <v>11.22</v>
+        <v>11.36</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.5163</v>
+        <v>46.7387</v>
       </c>
       <c r="J7" t="n">
-        <v>47466.16</v>
+        <v>47693.1</v>
       </c>
       <c r="K7" t="n">
-        <v>13.02</v>
+        <v>13.56</v>
       </c>
       <c r="L7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.9349</v>
+        <v>16.98</v>
       </c>
       <c r="J8" t="n">
-        <v>47463.68</v>
+        <v>47590.08</v>
       </c>
       <c r="K8" t="n">
-        <v>13.01</v>
+        <v>13.32</v>
       </c>
       <c r="L8" t="n">
-        <v>8.359999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>169.225</v>
+        <v>169.946</v>
       </c>
       <c r="J9" t="n">
-        <v>43686.79</v>
+        <v>43872.92</v>
       </c>
       <c r="K9" t="n">
-        <v>4.02</v>
+        <v>4.46</v>
       </c>
       <c r="L9" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,16 +11352,16 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1373.096</v>
+        <v>1381.605</v>
       </c>
       <c r="J10" t="n">
-        <v>19491.1</v>
+        <v>19611.88</v>
       </c>
       <c r="K10" t="n">
-        <v>282.81</v>
+        <v>285.18</v>
       </c>
       <c r="L10" t="n">
-        <v>17.79</v>
+        <v>17.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.748</v>
+        <v>11.83</v>
       </c>
       <c r="J11" t="n">
-        <v>47851.74</v>
+        <v>48185.74</v>
       </c>
       <c r="K11" t="n">
-        <v>13.94</v>
+        <v>14.73</v>
       </c>
       <c r="L11" t="n">
-        <v>8.710000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.732</v>
+        <v>27.7996</v>
       </c>
       <c r="J12" t="n">
-        <v>48612.28</v>
+        <v>48730.78</v>
       </c>
       <c r="K12" t="n">
-        <v>15.75</v>
+        <v>16.03</v>
       </c>
       <c r="L12" t="n">
-        <v>9.720000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.6211</v>
+        <v>22.4742</v>
       </c>
       <c r="J2" t="n">
-        <v>48572.86</v>
+        <v>48257.43</v>
       </c>
       <c r="K2" t="n">
-        <v>15.66</v>
+        <v>14.9</v>
       </c>
       <c r="L2" t="n">
-        <v>9.869999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,13 +10967,13 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>464.303</v>
+        <v>464.257</v>
       </c>
       <c r="J3" t="n">
-        <v>79890.3</v>
+        <v>79882.38</v>
       </c>
       <c r="K3" t="n">
-        <v>166.3</v>
+        <v>166.27</v>
       </c>
       <c r="L3" t="n">
         <v>13.93</v>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5571</v>
+        <v>12.5282</v>
       </c>
       <c r="J4" t="n">
-        <v>54694.09</v>
+        <v>54568.22</v>
       </c>
       <c r="K4" t="n">
-        <v>30.23</v>
+        <v>29.93</v>
       </c>
       <c r="L4" t="n">
-        <v>18.31</v>
+        <v>18.11</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>155.78</v>
+        <v>155.537</v>
       </c>
       <c r="J5" t="n">
-        <v>46369.47</v>
+        <v>46297.14</v>
       </c>
       <c r="K5" t="n">
-        <v>15.93</v>
+        <v>15.75</v>
       </c>
       <c r="L5" t="n">
-        <v>6.3</v>
+        <v>6.22</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4966.8626</v>
+        <v>4960.9406</v>
       </c>
       <c r="J6" t="n">
-        <v>49504.72</v>
+        <v>49445.69</v>
       </c>
       <c r="K6" t="n">
-        <v>17.87</v>
+        <v>17.73</v>
       </c>
       <c r="L6" t="n">
-        <v>11.36</v>
+        <v>11.25</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.7387</v>
+        <v>46.1645</v>
       </c>
       <c r="J7" t="n">
-        <v>47693.1</v>
+        <v>47107.18</v>
       </c>
       <c r="K7" t="n">
-        <v>13.56</v>
+        <v>12.17</v>
       </c>
       <c r="L7" t="n">
-        <v>8.52</v>
+        <v>7.64</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.98</v>
+        <v>16.8301</v>
       </c>
       <c r="J8" t="n">
-        <v>47590.08</v>
+        <v>47169.96</v>
       </c>
       <c r="K8" t="n">
-        <v>13.32</v>
+        <v>12.32</v>
       </c>
       <c r="L8" t="n">
-        <v>8.529999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>169.946</v>
+        <v>169.783</v>
       </c>
       <c r="J9" t="n">
-        <v>43872.92</v>
+        <v>43830.84</v>
       </c>
       <c r="K9" t="n">
-        <v>4.46</v>
+        <v>4.36</v>
       </c>
       <c r="L9" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1381.605</v>
+        <v>1384.309</v>
       </c>
       <c r="J10" t="n">
-        <v>19611.88</v>
+        <v>19650.27</v>
       </c>
       <c r="K10" t="n">
-        <v>285.18</v>
+        <v>285.94</v>
       </c>
       <c r="L10" t="n">
         <v>17.8</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.83</v>
+        <v>11.761</v>
       </c>
       <c r="J11" t="n">
-        <v>48185.74</v>
+        <v>47904.69</v>
       </c>
       <c r="K11" t="n">
-        <v>14.73</v>
+        <v>14.06</v>
       </c>
       <c r="L11" t="n">
-        <v>9.18</v>
+        <v>8.76</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.7996</v>
+        <v>27.7039</v>
       </c>
       <c r="J12" t="n">
-        <v>48730.78</v>
+        <v>48563.03</v>
       </c>
       <c r="K12" t="n">
-        <v>16.03</v>
+        <v>15.63</v>
       </c>
       <c r="L12" t="n">
-        <v>9.869999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.4742</v>
+        <v>22.1068</v>
       </c>
       <c r="J2" t="n">
-        <v>48257.43</v>
+        <v>47468.54</v>
       </c>
       <c r="K2" t="n">
-        <v>14.9</v>
+        <v>13.03</v>
       </c>
       <c r="L2" t="n">
-        <v>9.390000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>464.257</v>
+        <v>454.334</v>
       </c>
       <c r="J3" t="n">
-        <v>79882.38</v>
+        <v>78174.98</v>
       </c>
       <c r="K3" t="n">
-        <v>166.27</v>
+        <v>160.58</v>
       </c>
       <c r="L3" t="n">
-        <v>13.93</v>
+        <v>13.89</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5282</v>
+        <v>12.3454</v>
       </c>
       <c r="J4" t="n">
-        <v>54568.22</v>
+        <v>53772.01</v>
       </c>
       <c r="K4" t="n">
-        <v>29.93</v>
+        <v>28.03</v>
       </c>
       <c r="L4" t="n">
-        <v>18.11</v>
+        <v>16.98</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>155.537</v>
+        <v>152.627</v>
       </c>
       <c r="J5" t="n">
-        <v>46297.14</v>
+        <v>45430.95</v>
       </c>
       <c r="K5" t="n">
-        <v>15.75</v>
+        <v>13.58</v>
       </c>
       <c r="L5" t="n">
-        <v>6.22</v>
+        <v>5.39</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4960.9406</v>
+        <v>4886.889</v>
       </c>
       <c r="J6" t="n">
-        <v>49445.69</v>
+        <v>48707.62</v>
       </c>
       <c r="K6" t="n">
-        <v>17.73</v>
+        <v>15.98</v>
       </c>
       <c r="L6" t="n">
-        <v>11.25</v>
+        <v>10.15</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.1645</v>
+        <v>45.5855</v>
       </c>
       <c r="J7" t="n">
-        <v>47107.18</v>
+        <v>46516.36</v>
       </c>
       <c r="K7" t="n">
-        <v>12.17</v>
+        <v>10.76</v>
       </c>
       <c r="L7" t="n">
-        <v>7.64</v>
+        <v>6.76</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.8301</v>
+        <v>16.5604</v>
       </c>
       <c r="J8" t="n">
-        <v>47169.96</v>
+        <v>46414.06</v>
       </c>
       <c r="K8" t="n">
-        <v>12.32</v>
+        <v>10.52</v>
       </c>
       <c r="L8" t="n">
-        <v>7.89</v>
+        <v>6.75</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>169.783</v>
+        <v>166.618</v>
       </c>
       <c r="J9" t="n">
-        <v>43830.84</v>
+        <v>43013.77</v>
       </c>
       <c r="K9" t="n">
-        <v>4.36</v>
+        <v>2.42</v>
       </c>
       <c r="L9" t="n">
-        <v>2.79</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,16 +11352,16 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1384.309</v>
+        <v>1354.039</v>
       </c>
       <c r="J10" t="n">
-        <v>19650.27</v>
+        <v>19220.58</v>
       </c>
       <c r="K10" t="n">
-        <v>285.94</v>
+        <v>277.5</v>
       </c>
       <c r="L10" t="n">
-        <v>17.8</v>
+        <v>17.79</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.761</v>
+        <v>11.552</v>
       </c>
       <c r="J11" t="n">
-        <v>47904.69</v>
+        <v>47053.4</v>
       </c>
       <c r="K11" t="n">
-        <v>14.06</v>
+        <v>12.04</v>
       </c>
       <c r="L11" t="n">
-        <v>8.76</v>
+        <v>7.51</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.7039</v>
+        <v>27.1036</v>
       </c>
       <c r="J12" t="n">
-        <v>48563.03</v>
+        <v>47510.74</v>
       </c>
       <c r="K12" t="n">
-        <v>15.63</v>
+        <v>13.13</v>
       </c>
       <c r="L12" t="n">
-        <v>9.609999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.1068</v>
+        <v>22.7697</v>
       </c>
       <c r="J2" t="n">
-        <v>47468.54</v>
+        <v>48891.94</v>
       </c>
       <c r="K2" t="n">
-        <v>13.03</v>
+        <v>16.42</v>
       </c>
       <c r="L2" t="n">
-        <v>8.220000000000001</v>
+        <v>10.21</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>454.334</v>
+        <v>461.098</v>
       </c>
       <c r="J3" t="n">
-        <v>78174.98</v>
+        <v>79338.83</v>
       </c>
       <c r="K3" t="n">
-        <v>160.58</v>
+        <v>164.46</v>
       </c>
       <c r="L3" t="n">
-        <v>13.89</v>
+        <v>13.91</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.3454</v>
+        <v>12.5098</v>
       </c>
       <c r="J4" t="n">
-        <v>53772.01</v>
+        <v>54488.07</v>
       </c>
       <c r="K4" t="n">
-        <v>28.03</v>
+        <v>29.74</v>
       </c>
       <c r="L4" t="n">
-        <v>16.98</v>
+        <v>17.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>152.627</v>
+        <v>154.56</v>
       </c>
       <c r="J5" t="n">
-        <v>45430.95</v>
+        <v>46006.33</v>
       </c>
       <c r="K5" t="n">
-        <v>13.58</v>
+        <v>15.02</v>
       </c>
       <c r="L5" t="n">
-        <v>5.39</v>
+        <v>5.91</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4886.889</v>
+        <v>4993.2106</v>
       </c>
       <c r="J6" t="n">
-        <v>48707.62</v>
+        <v>49767.33</v>
       </c>
       <c r="K6" t="n">
-        <v>15.98</v>
+        <v>18.5</v>
       </c>
       <c r="L6" t="n">
-        <v>10.15</v>
+        <v>11.59</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>45.5855</v>
+        <v>46.9559</v>
       </c>
       <c r="J7" t="n">
-        <v>46516.36</v>
+        <v>47914.74</v>
       </c>
       <c r="K7" t="n">
-        <v>10.76</v>
+        <v>14.09</v>
       </c>
       <c r="L7" t="n">
-        <v>6.76</v>
+        <v>8.73</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.5604</v>
+        <v>16.9952</v>
       </c>
       <c r="J8" t="n">
-        <v>46414.06</v>
+        <v>47632.68</v>
       </c>
       <c r="K8" t="n">
-        <v>10.52</v>
+        <v>13.42</v>
       </c>
       <c r="L8" t="n">
-        <v>6.75</v>
+        <v>8.49</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>166.618</v>
+        <v>168.774</v>
       </c>
       <c r="J9" t="n">
-        <v>43013.77</v>
+        <v>43570.36</v>
       </c>
       <c r="K9" t="n">
-        <v>2.42</v>
+        <v>3.74</v>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>2.37</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1354.039</v>
+        <v>1375.913</v>
       </c>
       <c r="J10" t="n">
-        <v>19220.58</v>
+        <v>19531.09</v>
       </c>
       <c r="K10" t="n">
-        <v>277.5</v>
+        <v>283.6</v>
       </c>
       <c r="L10" t="n">
         <v>17.79</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.552</v>
+        <v>11.771</v>
       </c>
       <c r="J11" t="n">
-        <v>47053.4</v>
+        <v>47945.43</v>
       </c>
       <c r="K11" t="n">
-        <v>12.04</v>
+        <v>14.16</v>
       </c>
       <c r="L11" t="n">
-        <v>7.51</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.1036</v>
+        <v>27.7393</v>
       </c>
       <c r="J12" t="n">
-        <v>47510.74</v>
+        <v>48625.08</v>
       </c>
       <c r="K12" t="n">
-        <v>13.13</v>
+        <v>15.78</v>
       </c>
       <c r="L12" t="n">
-        <v>8.09</v>
+        <v>9.59</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.7697</v>
+        <v>22.6413</v>
       </c>
       <c r="J2" t="n">
-        <v>48891.94</v>
+        <v>48616.24</v>
       </c>
       <c r="K2" t="n">
-        <v>16.42</v>
+        <v>15.76</v>
       </c>
       <c r="L2" t="n">
-        <v>10.21</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>461.098</v>
+        <v>457.37</v>
       </c>
       <c r="J3" t="n">
-        <v>79338.83</v>
+        <v>78697.37</v>
       </c>
       <c r="K3" t="n">
-        <v>164.46</v>
+        <v>162.32</v>
       </c>
       <c r="L3" t="n">
-        <v>13.91</v>
+        <v>13.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5098</v>
+        <v>12.3661</v>
       </c>
       <c r="J4" t="n">
-        <v>54488.07</v>
+        <v>53862.17</v>
       </c>
       <c r="K4" t="n">
-        <v>29.74</v>
+        <v>28.25</v>
       </c>
       <c r="L4" t="n">
-        <v>17.8</v>
+        <v>16.91</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>154.56</v>
+        <v>153.641</v>
       </c>
       <c r="J5" t="n">
-        <v>46006.33</v>
+        <v>45732.78</v>
       </c>
       <c r="K5" t="n">
-        <v>15.02</v>
+        <v>14.34</v>
       </c>
       <c r="L5" t="n">
-        <v>5.91</v>
+        <v>5.64</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4993.2106</v>
+        <v>4968.318</v>
       </c>
       <c r="J6" t="n">
-        <v>49767.33</v>
+        <v>49519.23</v>
       </c>
       <c r="K6" t="n">
-        <v>18.5</v>
+        <v>17.91</v>
       </c>
       <c r="L6" t="n">
-        <v>11.59</v>
+        <v>11.21</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.9559</v>
+        <v>46.9926</v>
       </c>
       <c r="J7" t="n">
-        <v>47914.74</v>
+        <v>47952.19</v>
       </c>
       <c r="K7" t="n">
-        <v>14.09</v>
+        <v>14.18</v>
       </c>
       <c r="L7" t="n">
-        <v>8.73</v>
+        <v>8.76</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.9952</v>
+        <v>17.0443</v>
       </c>
       <c r="J8" t="n">
-        <v>47632.68</v>
+        <v>47770.3</v>
       </c>
       <c r="K8" t="n">
-        <v>13.42</v>
+        <v>13.74</v>
       </c>
       <c r="L8" t="n">
-        <v>8.49</v>
+        <v>8.67</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>168.774</v>
+        <v>167.68</v>
       </c>
       <c r="J9" t="n">
-        <v>43570.36</v>
+        <v>43287.93</v>
       </c>
       <c r="K9" t="n">
-        <v>3.74</v>
+        <v>3.07</v>
       </c>
       <c r="L9" t="n">
-        <v>2.37</v>
+        <v>1.94</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1375.913</v>
+        <v>1365.621</v>
       </c>
       <c r="J10" t="n">
-        <v>19531.09</v>
+        <v>19384.99</v>
       </c>
       <c r="K10" t="n">
-        <v>283.6</v>
+        <v>280.73</v>
       </c>
       <c r="L10" t="n">
         <v>17.79</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.771</v>
+        <v>11.716</v>
       </c>
       <c r="J11" t="n">
-        <v>47945.43</v>
+        <v>47721.4</v>
       </c>
       <c r="K11" t="n">
-        <v>14.16</v>
+        <v>13.63</v>
       </c>
       <c r="L11" t="n">
-        <v>8.720000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.7393</v>
+        <v>27.475</v>
       </c>
       <c r="J12" t="n">
-        <v>48625.08</v>
+        <v>48161.78</v>
       </c>
       <c r="K12" t="n">
-        <v>15.78</v>
+        <v>14.68</v>
       </c>
       <c r="L12" t="n">
-        <v>9.59</v>
+        <v>8.92</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.6413</v>
+        <v>22.7357</v>
       </c>
       <c r="J2" t="n">
-        <v>48616.24</v>
+        <v>48818.94</v>
       </c>
       <c r="K2" t="n">
-        <v>15.76</v>
+        <v>16.24</v>
       </c>
       <c r="L2" t="n">
-        <v>9.789999999999999</v>
+        <v>10.06</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,13 +10967,13 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>457.37</v>
+        <v>458.29</v>
       </c>
       <c r="J3" t="n">
-        <v>78697.37</v>
+        <v>78855.67</v>
       </c>
       <c r="K3" t="n">
-        <v>162.32</v>
+        <v>162.85</v>
       </c>
       <c r="L3" t="n">
         <v>13.9</v>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.3661</v>
+        <v>12.4728</v>
       </c>
       <c r="J4" t="n">
-        <v>53862.17</v>
+        <v>54326.91</v>
       </c>
       <c r="K4" t="n">
-        <v>28.25</v>
+        <v>29.36</v>
       </c>
       <c r="L4" t="n">
-        <v>16.91</v>
+        <v>17.51</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>153.641</v>
+        <v>153.885</v>
       </c>
       <c r="J5" t="n">
-        <v>45732.78</v>
+        <v>45805.41</v>
       </c>
       <c r="K5" t="n">
-        <v>14.34</v>
+        <v>14.52</v>
       </c>
       <c r="L5" t="n">
-        <v>5.64</v>
+        <v>5.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4968.318</v>
+        <v>4996.3095</v>
       </c>
       <c r="J6" t="n">
-        <v>49519.23</v>
+        <v>49798.22</v>
       </c>
       <c r="K6" t="n">
-        <v>17.91</v>
+        <v>18.57</v>
       </c>
       <c r="L6" t="n">
-        <v>11.21</v>
+        <v>11.59</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.9926</v>
+        <v>46.6938</v>
       </c>
       <c r="J7" t="n">
-        <v>47952.19</v>
+        <v>47647.29</v>
       </c>
       <c r="K7" t="n">
-        <v>14.18</v>
+        <v>13.45</v>
       </c>
       <c r="L7" t="n">
-        <v>8.76</v>
+        <v>8.31</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>17.0443</v>
+        <v>17.0077</v>
       </c>
       <c r="J8" t="n">
-        <v>47770.3</v>
+        <v>47667.72</v>
       </c>
       <c r="K8" t="n">
-        <v>13.74</v>
+        <v>13.5</v>
       </c>
       <c r="L8" t="n">
-        <v>8.67</v>
+        <v>8.51</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>167.68</v>
+        <v>167.92</v>
       </c>
       <c r="J9" t="n">
-        <v>43287.93</v>
+        <v>43349.89</v>
       </c>
       <c r="K9" t="n">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="L9" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1365.621</v>
+        <v>1370.314</v>
       </c>
       <c r="J10" t="n">
-        <v>19384.99</v>
+        <v>19451.61</v>
       </c>
       <c r="K10" t="n">
-        <v>280.73</v>
+        <v>282.04</v>
       </c>
       <c r="L10" t="n">
         <v>17.79</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.716</v>
+        <v>11.778</v>
       </c>
       <c r="J11" t="n">
-        <v>47721.4</v>
+        <v>47973.94</v>
       </c>
       <c r="K11" t="n">
-        <v>13.63</v>
+        <v>14.23</v>
       </c>
       <c r="L11" t="n">
-        <v>8.390000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.475</v>
+        <v>27.5924</v>
       </c>
       <c r="J12" t="n">
-        <v>48161.78</v>
+        <v>48367.57</v>
       </c>
       <c r="K12" t="n">
-        <v>14.68</v>
+        <v>15.17</v>
       </c>
       <c r="L12" t="n">
-        <v>8.92</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.7357</v>
+        <v>22.707</v>
       </c>
       <c r="J2" t="n">
-        <v>48818.94</v>
+        <v>48757.31</v>
       </c>
       <c r="K2" t="n">
-        <v>16.24</v>
+        <v>16.09</v>
       </c>
       <c r="L2" t="n">
-        <v>10.06</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,13 +10967,13 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>458.29</v>
+        <v>457.882</v>
       </c>
       <c r="J3" t="n">
-        <v>78855.67</v>
+        <v>78785.47</v>
       </c>
       <c r="K3" t="n">
-        <v>162.85</v>
+        <v>162.62</v>
       </c>
       <c r="L3" t="n">
         <v>13.9</v>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.4728</v>
+        <v>12.5037</v>
       </c>
       <c r="J4" t="n">
-        <v>54326.91</v>
+        <v>54461.5</v>
       </c>
       <c r="K4" t="n">
-        <v>29.36</v>
+        <v>29.68</v>
       </c>
       <c r="L4" t="n">
-        <v>17.51</v>
+        <v>17.66</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>153.885</v>
+        <v>153.451</v>
       </c>
       <c r="J5" t="n">
-        <v>45805.41</v>
+        <v>45676.22</v>
       </c>
       <c r="K5" t="n">
-        <v>14.52</v>
+        <v>14.2</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.58</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4996.3095</v>
+        <v>4967.7903</v>
       </c>
       <c r="J6" t="n">
-        <v>49798.22</v>
+        <v>49513.97</v>
       </c>
       <c r="K6" t="n">
-        <v>18.57</v>
+        <v>17.9</v>
       </c>
       <c r="L6" t="n">
-        <v>11.59</v>
+        <v>11.16</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.6938</v>
+        <v>46.7494</v>
       </c>
       <c r="J7" t="n">
-        <v>47647.29</v>
+        <v>47704.02</v>
       </c>
       <c r="K7" t="n">
-        <v>13.45</v>
+        <v>13.59</v>
       </c>
       <c r="L7" t="n">
-        <v>8.31</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>17.0077</v>
+        <v>17.055</v>
       </c>
       <c r="J8" t="n">
-        <v>47667.72</v>
+        <v>47800.29</v>
       </c>
       <c r="K8" t="n">
-        <v>13.5</v>
+        <v>13.82</v>
       </c>
       <c r="L8" t="n">
-        <v>8.51</v>
+        <v>8.69</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>167.92</v>
+        <v>167.445</v>
       </c>
       <c r="J9" t="n">
-        <v>43349.89</v>
+        <v>43227.27</v>
       </c>
       <c r="K9" t="n">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="L9" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1370.314</v>
+        <v>1368.067</v>
       </c>
       <c r="J10" t="n">
-        <v>19451.61</v>
+        <v>19419.71</v>
       </c>
       <c r="K10" t="n">
-        <v>282.04</v>
+        <v>281.41</v>
       </c>
       <c r="L10" t="n">
         <v>17.79</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.778</v>
+        <v>11.858</v>
       </c>
       <c r="J11" t="n">
-        <v>47973.94</v>
+        <v>48299.79</v>
       </c>
       <c r="K11" t="n">
-        <v>14.23</v>
+        <v>15.01</v>
       </c>
       <c r="L11" t="n">
-        <v>8.73</v>
+        <v>9.18</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.5924</v>
+        <v>27.5676</v>
       </c>
       <c r="J12" t="n">
-        <v>48367.57</v>
+        <v>48324.1</v>
       </c>
       <c r="K12" t="n">
-        <v>15.17</v>
+        <v>15.06</v>
       </c>
       <c r="L12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.707</v>
+        <v>22.5939</v>
       </c>
       <c r="J2" t="n">
-        <v>48757.31</v>
+        <v>48514.46</v>
       </c>
       <c r="K2" t="n">
-        <v>16.09</v>
+        <v>15.52</v>
       </c>
       <c r="L2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>457.882</v>
+        <v>461.394</v>
       </c>
       <c r="J3" t="n">
-        <v>78785.47</v>
+        <v>79389.75999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>162.62</v>
+        <v>164.63</v>
       </c>
       <c r="L3" t="n">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5037</v>
+        <v>12.5868</v>
       </c>
       <c r="J4" t="n">
-        <v>54461.5</v>
+        <v>54823.46</v>
       </c>
       <c r="K4" t="n">
-        <v>29.68</v>
+        <v>30.54</v>
       </c>
       <c r="L4" t="n">
-        <v>17.66</v>
+        <v>18.11</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>153.451</v>
+        <v>154.462</v>
       </c>
       <c r="J5" t="n">
-        <v>45676.22</v>
+        <v>45977.16</v>
       </c>
       <c r="K5" t="n">
-        <v>14.2</v>
+        <v>14.95</v>
       </c>
       <c r="L5" t="n">
-        <v>5.58</v>
+        <v>5.85</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4967.7903</v>
+        <v>4945.9003</v>
       </c>
       <c r="J6" t="n">
-        <v>49513.97</v>
+        <v>49295.79</v>
       </c>
       <c r="K6" t="n">
-        <v>17.9</v>
+        <v>17.38</v>
       </c>
       <c r="L6" t="n">
-        <v>11.16</v>
+        <v>10.83</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.7494</v>
+        <v>46.6854</v>
       </c>
       <c r="J7" t="n">
-        <v>47704.02</v>
+        <v>47638.72</v>
       </c>
       <c r="K7" t="n">
-        <v>13.59</v>
+        <v>13.43</v>
       </c>
       <c r="L7" t="n">
-        <v>8.380000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>17.055</v>
+        <v>17.1312</v>
       </c>
       <c r="J8" t="n">
-        <v>47800.29</v>
+        <v>48013.85</v>
       </c>
       <c r="K8" t="n">
-        <v>13.82</v>
+        <v>14.32</v>
       </c>
       <c r="L8" t="n">
-        <v>8.69</v>
+        <v>8.98</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>167.445</v>
+        <v>168.459</v>
       </c>
       <c r="J9" t="n">
-        <v>43227.27</v>
+        <v>43489.04</v>
       </c>
       <c r="K9" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1368.067</v>
+        <v>1377.978</v>
       </c>
       <c r="J10" t="n">
-        <v>19419.71</v>
+        <v>19560.4</v>
       </c>
       <c r="K10" t="n">
-        <v>281.41</v>
+        <v>284.17</v>
       </c>
       <c r="L10" t="n">
         <v>17.79</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.858</v>
+        <v>11.844</v>
       </c>
       <c r="J11" t="n">
-        <v>48299.79</v>
+        <v>48242.77</v>
       </c>
       <c r="K11" t="n">
-        <v>15.01</v>
+        <v>14.87</v>
       </c>
       <c r="L11" t="n">
-        <v>9.18</v>
+        <v>9.08</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.5676</v>
+        <v>27.6139</v>
       </c>
       <c r="J12" t="n">
-        <v>48324.1</v>
+        <v>48405.26</v>
       </c>
       <c r="K12" t="n">
-        <v>15.06</v>
+        <v>15.26</v>
       </c>
       <c r="L12" t="n">
-        <v>9.119999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10921,7 +10921,7 @@
         <v>15.52</v>
       </c>
       <c r="L2" t="n">
-        <v>9.59</v>
+        <v>9.57</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>30.54</v>
       </c>
       <c r="L4" t="n">
-        <v>18.11</v>
+        <v>18.08</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>17.38</v>
       </c>
       <c r="L6" t="n">
-        <v>10.83</v>
+        <v>10.81</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>13.43</v>
       </c>
       <c r="L7" t="n">
-        <v>8.27</v>
+        <v>8.25</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>14.32</v>
       </c>
       <c r="L8" t="n">
-        <v>8.98</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>14.87</v>
       </c>
       <c r="L11" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>15.26</v>
       </c>
       <c r="L12" t="n">
-        <v>9.220000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10921,7 +10921,7 @@
         <v>15.52</v>
       </c>
       <c r="L2" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>30.54</v>
       </c>
       <c r="L4" t="n">
-        <v>18.08</v>
+        <v>18.05</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>14.95</v>
       </c>
       <c r="L5" t="n">
-        <v>5.85</v>
+        <v>5.84</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>17.38</v>
       </c>
       <c r="L6" t="n">
-        <v>10.81</v>
+        <v>10.79</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>13.43</v>
       </c>
       <c r="L7" t="n">
-        <v>8.25</v>
+        <v>8.24</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>14.32</v>
       </c>
       <c r="L8" t="n">
-        <v>8.960000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>14.87</v>
       </c>
       <c r="L11" t="n">
-        <v>9.07</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>15.26</v>
       </c>
       <c r="L12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.5939</v>
+        <v>22.7511</v>
       </c>
       <c r="J2" t="n">
-        <v>48514.46</v>
+        <v>48852</v>
       </c>
       <c r="K2" t="n">
-        <v>15.52</v>
+        <v>16.32</v>
       </c>
       <c r="L2" t="n">
-        <v>9.56</v>
+        <v>10.02</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>461.394</v>
+        <v>459.134</v>
       </c>
       <c r="J3" t="n">
-        <v>79389.75999999999</v>
+        <v>79000.89</v>
       </c>
       <c r="K3" t="n">
-        <v>164.63</v>
+        <v>163.34</v>
       </c>
       <c r="L3" t="n">
-        <v>13.91</v>
+        <v>13.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5868</v>
+        <v>12.5974</v>
       </c>
       <c r="J4" t="n">
-        <v>54823.46</v>
+        <v>54869.63</v>
       </c>
       <c r="K4" t="n">
-        <v>30.54</v>
+        <v>30.65</v>
       </c>
       <c r="L4" t="n">
-        <v>18.05</v>
+        <v>18.08</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>154.462</v>
+        <v>153.57</v>
       </c>
       <c r="J5" t="n">
-        <v>45977.16</v>
+        <v>45711.65</v>
       </c>
       <c r="K5" t="n">
-        <v>14.95</v>
+        <v>14.28</v>
       </c>
       <c r="L5" t="n">
-        <v>5.84</v>
+        <v>5.58</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4945.9003</v>
+        <v>4967.8773</v>
       </c>
       <c r="J6" t="n">
-        <v>49295.79</v>
+        <v>49514.83</v>
       </c>
       <c r="K6" t="n">
-        <v>17.38</v>
+        <v>17.9</v>
       </c>
       <c r="L6" t="n">
-        <v>10.79</v>
+        <v>11.08</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.6854</v>
+        <v>46.8685</v>
       </c>
       <c r="J7" t="n">
-        <v>47638.72</v>
+        <v>47825.55</v>
       </c>
       <c r="K7" t="n">
-        <v>13.43</v>
+        <v>13.88</v>
       </c>
       <c r="L7" t="n">
-        <v>8.24</v>
+        <v>8.49</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>17.1312</v>
+        <v>17.1505</v>
       </c>
       <c r="J8" t="n">
-        <v>48013.85</v>
+        <v>48067.95</v>
       </c>
       <c r="K8" t="n">
-        <v>14.32</v>
+        <v>14.45</v>
       </c>
       <c r="L8" t="n">
-        <v>8.949999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>168.459</v>
+        <v>167.684</v>
       </c>
       <c r="J9" t="n">
-        <v>43489.04</v>
+        <v>43288.97</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.07</v>
       </c>
       <c r="L9" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1377.978</v>
+        <v>1371.192</v>
       </c>
       <c r="J10" t="n">
-        <v>19560.4</v>
+        <v>19464.07</v>
       </c>
       <c r="K10" t="n">
-        <v>284.17</v>
+        <v>282.28</v>
       </c>
       <c r="L10" t="n">
         <v>17.79</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.844</v>
+        <v>11.888</v>
       </c>
       <c r="J11" t="n">
-        <v>48242.77</v>
+        <v>48421.99</v>
       </c>
       <c r="K11" t="n">
-        <v>14.87</v>
+        <v>15.3</v>
       </c>
       <c r="L11" t="n">
-        <v>9.050000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.6139</v>
+        <v>27.9554</v>
       </c>
       <c r="J12" t="n">
-        <v>48405.26</v>
+        <v>49003.89</v>
       </c>
       <c r="K12" t="n">
-        <v>15.26</v>
+        <v>16.68</v>
       </c>
       <c r="L12" t="n">
-        <v>9.19</v>
+        <v>10</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.7511</v>
+        <v>22.6182</v>
       </c>
       <c r="J2" t="n">
-        <v>48852</v>
+        <v>48566.64</v>
       </c>
       <c r="K2" t="n">
-        <v>16.32</v>
+        <v>15.64</v>
       </c>
       <c r="L2" t="n">
-        <v>10.02</v>
+        <v>9.58</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>459.134</v>
+        <v>454.291</v>
       </c>
       <c r="J3" t="n">
-        <v>79000.89</v>
+        <v>78167.58</v>
       </c>
       <c r="K3" t="n">
-        <v>163.34</v>
+        <v>160.56</v>
       </c>
       <c r="L3" t="n">
-        <v>13.9</v>
+        <v>13.88</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5974</v>
+        <v>12.6639</v>
       </c>
       <c r="J4" t="n">
-        <v>54869.63</v>
+        <v>55159.28</v>
       </c>
       <c r="K4" t="n">
-        <v>30.65</v>
+        <v>31.34</v>
       </c>
       <c r="L4" t="n">
-        <v>18.08</v>
+        <v>18.39</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>153.57</v>
+        <v>153.225</v>
       </c>
       <c r="J5" t="n">
-        <v>45711.65</v>
+        <v>45608.95</v>
       </c>
       <c r="K5" t="n">
-        <v>14.28</v>
+        <v>14.03</v>
       </c>
       <c r="L5" t="n">
-        <v>5.58</v>
+        <v>5.47</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4967.8773</v>
+        <v>4927.5417</v>
       </c>
       <c r="J6" t="n">
-        <v>49514.83</v>
+        <v>49112.81</v>
       </c>
       <c r="K6" t="n">
-        <v>17.9</v>
+        <v>16.94</v>
       </c>
       <c r="L6" t="n">
-        <v>11.08</v>
+        <v>10.47</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.8685</v>
+        <v>46.1191</v>
       </c>
       <c r="J7" t="n">
-        <v>47825.55</v>
+        <v>47060.85</v>
       </c>
       <c r="K7" t="n">
-        <v>13.88</v>
+        <v>12.06</v>
       </c>
       <c r="L7" t="n">
-        <v>8.49</v>
+        <v>7.37</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>17.1505</v>
+        <v>16.9209</v>
       </c>
       <c r="J8" t="n">
-        <v>48067.95</v>
+        <v>47424.44</v>
       </c>
       <c r="K8" t="n">
-        <v>14.45</v>
+        <v>12.92</v>
       </c>
       <c r="L8" t="n">
-        <v>9.01</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>167.684</v>
+        <v>167.076</v>
       </c>
       <c r="J9" t="n">
-        <v>43288.97</v>
+        <v>43132.01</v>
       </c>
       <c r="K9" t="n">
-        <v>3.07</v>
+        <v>2.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,16 +11352,16 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1371.192</v>
+        <v>1360.009</v>
       </c>
       <c r="J10" t="n">
-        <v>19464.07</v>
+        <v>19305.33</v>
       </c>
       <c r="K10" t="n">
-        <v>282.28</v>
+        <v>279.16</v>
       </c>
       <c r="L10" t="n">
-        <v>17.79</v>
+        <v>17.78</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.888</v>
+        <v>11.812</v>
       </c>
       <c r="J11" t="n">
-        <v>48421.99</v>
+        <v>48112.43</v>
       </c>
       <c r="K11" t="n">
-        <v>15.3</v>
+        <v>14.56</v>
       </c>
       <c r="L11" t="n">
-        <v>9.289999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.9554</v>
+        <v>27.6248</v>
       </c>
       <c r="J12" t="n">
-        <v>49003.89</v>
+        <v>48424.37</v>
       </c>
       <c r="K12" t="n">
-        <v>16.68</v>
+        <v>15.3</v>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>9.16</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.6182</v>
+        <v>22.4209</v>
       </c>
       <c r="J2" t="n">
-        <v>48566.64</v>
+        <v>48142.99</v>
       </c>
       <c r="K2" t="n">
-        <v>15.64</v>
+        <v>14.63</v>
       </c>
       <c r="L2" t="n">
-        <v>9.58</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>454.291</v>
+        <v>452.831</v>
       </c>
       <c r="J3" t="n">
-        <v>78167.58</v>
+        <v>77916.37</v>
       </c>
       <c r="K3" t="n">
-        <v>160.56</v>
+        <v>159.72</v>
       </c>
       <c r="L3" t="n">
-        <v>13.88</v>
+        <v>13.87</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.6639</v>
+        <v>12.6511</v>
       </c>
       <c r="J4" t="n">
-        <v>55159.28</v>
+        <v>55103.52</v>
       </c>
       <c r="K4" t="n">
-        <v>31.34</v>
+        <v>31.21</v>
       </c>
       <c r="L4" t="n">
-        <v>18.39</v>
+        <v>18.29</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>153.225</v>
+        <v>152.677</v>
       </c>
       <c r="J5" t="n">
-        <v>45608.95</v>
+        <v>45445.84</v>
       </c>
       <c r="K5" t="n">
-        <v>14.03</v>
+        <v>13.62</v>
       </c>
       <c r="L5" t="n">
-        <v>5.47</v>
+        <v>5.32</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4927.5417</v>
+        <v>4895.9757</v>
       </c>
       <c r="J6" t="n">
-        <v>49112.81</v>
+        <v>48798.19</v>
       </c>
       <c r="K6" t="n">
-        <v>16.94</v>
+        <v>16.19</v>
       </c>
       <c r="L6" t="n">
-        <v>10.47</v>
+        <v>10</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.1191</v>
+        <v>45.4064</v>
       </c>
       <c r="J7" t="n">
-        <v>47060.85</v>
+        <v>46333.6</v>
       </c>
       <c r="K7" t="n">
-        <v>12.06</v>
+        <v>10.32</v>
       </c>
       <c r="L7" t="n">
-        <v>7.37</v>
+        <v>6.32</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.9209</v>
+        <v>16.7037</v>
       </c>
       <c r="J8" t="n">
-        <v>47424.44</v>
+        <v>46815.69</v>
       </c>
       <c r="K8" t="n">
-        <v>12.92</v>
+        <v>11.47</v>
       </c>
       <c r="L8" t="n">
-        <v>8.050000000000001</v>
+        <v>7.15</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>167.076</v>
+        <v>166.291</v>
       </c>
       <c r="J9" t="n">
-        <v>43132.01</v>
+        <v>42929.35</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>2.22</v>
       </c>
       <c r="L9" t="n">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1360.009</v>
+        <v>1354.628</v>
       </c>
       <c r="J10" t="n">
-        <v>19305.33</v>
+        <v>19228.94</v>
       </c>
       <c r="K10" t="n">
-        <v>279.16</v>
+        <v>277.66</v>
       </c>
       <c r="L10" t="n">
         <v>17.78</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.812</v>
+        <v>11.706</v>
       </c>
       <c r="J11" t="n">
-        <v>48112.43</v>
+        <v>47680.67</v>
       </c>
       <c r="K11" t="n">
-        <v>14.56</v>
+        <v>13.53</v>
       </c>
       <c r="L11" t="n">
-        <v>8.82</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.6248</v>
+        <v>27.3426</v>
       </c>
       <c r="J12" t="n">
-        <v>48424.37</v>
+        <v>47929.69</v>
       </c>
       <c r="K12" t="n">
-        <v>15.3</v>
+        <v>14.12</v>
       </c>
       <c r="L12" t="n">
-        <v>9.16</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.4209</v>
+        <v>22.433</v>
       </c>
       <c r="J2" t="n">
-        <v>48142.99</v>
+        <v>48168.97</v>
       </c>
       <c r="K2" t="n">
-        <v>14.63</v>
+        <v>14.69</v>
       </c>
       <c r="L2" t="n">
-        <v>8.960000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,13 +10967,13 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>452.831</v>
+        <v>452.213</v>
       </c>
       <c r="J3" t="n">
-        <v>77916.37</v>
+        <v>77810.03</v>
       </c>
       <c r="K3" t="n">
-        <v>159.72</v>
+        <v>159.37</v>
       </c>
       <c r="L3" t="n">
         <v>13.87</v>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.6511</v>
+        <v>12.5741</v>
       </c>
       <c r="J4" t="n">
-        <v>55103.52</v>
+        <v>54768.14</v>
       </c>
       <c r="K4" t="n">
-        <v>31.21</v>
+        <v>30.41</v>
       </c>
       <c r="L4" t="n">
-        <v>18.29</v>
+        <v>17.81</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>152.677</v>
+        <v>152.461</v>
       </c>
       <c r="J5" t="n">
-        <v>45445.84</v>
+        <v>45381.54</v>
       </c>
       <c r="K5" t="n">
-        <v>13.62</v>
+        <v>13.46</v>
       </c>
       <c r="L5" t="n">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4895.9757</v>
+        <v>4893.7136</v>
       </c>
       <c r="J6" t="n">
-        <v>48798.19</v>
+        <v>48775.64</v>
       </c>
       <c r="K6" t="n">
-        <v>16.19</v>
+        <v>16.14</v>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>45.4064</v>
+        <v>45.6192</v>
       </c>
       <c r="J7" t="n">
-        <v>46333.6</v>
+        <v>46550.74</v>
       </c>
       <c r="K7" t="n">
-        <v>10.32</v>
+        <v>10.84</v>
       </c>
       <c r="L7" t="n">
-        <v>6.32</v>
+        <v>6.62</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.7037</v>
+        <v>16.6985</v>
       </c>
       <c r="J8" t="n">
-        <v>46815.69</v>
+        <v>46801.12</v>
       </c>
       <c r="K8" t="n">
-        <v>11.47</v>
+        <v>11.44</v>
       </c>
       <c r="L8" t="n">
-        <v>7.15</v>
+        <v>7.11</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>166.291</v>
+        <v>166.164</v>
       </c>
       <c r="J9" t="n">
-        <v>42929.35</v>
+        <v>42896.57</v>
       </c>
       <c r="K9" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1354.628</v>
+        <v>1355.492</v>
       </c>
       <c r="J10" t="n">
-        <v>19228.94</v>
+        <v>19241.21</v>
       </c>
       <c r="K10" t="n">
-        <v>277.66</v>
+        <v>277.9</v>
       </c>
       <c r="L10" t="n">
         <v>17.78</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.706</v>
+        <v>11.686</v>
       </c>
       <c r="J11" t="n">
-        <v>47680.67</v>
+        <v>47599.2</v>
       </c>
       <c r="K11" t="n">
-        <v>13.53</v>
+        <v>13.34</v>
       </c>
       <c r="L11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.3426</v>
+        <v>27.3001</v>
       </c>
       <c r="J12" t="n">
-        <v>47929.69</v>
+        <v>47855.19</v>
       </c>
       <c r="K12" t="n">
-        <v>14.12</v>
+        <v>13.95</v>
       </c>
       <c r="L12" t="n">
-        <v>8.460000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10921,7 +10921,7 @@
         <v>14.69</v>
       </c>
       <c r="L2" t="n">
-        <v>8.98</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>30.41</v>
       </c>
       <c r="L4" t="n">
-        <v>17.81</v>
+        <v>17.78</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>13.46</v>
       </c>
       <c r="L5" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>16.14</v>
       </c>
       <c r="L6" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>10.84</v>
       </c>
       <c r="L7" t="n">
-        <v>6.62</v>
+        <v>6.61</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>11.44</v>
       </c>
       <c r="L8" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>13.34</v>
       </c>
       <c r="L11" t="n">
-        <v>8.07</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>13.95</v>
       </c>
       <c r="L12" t="n">
-        <v>8.34</v>
+        <v>8.33</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10921,7 +10921,7 @@
         <v>14.69</v>
       </c>
       <c r="L2" t="n">
-        <v>8.960000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>30.41</v>
       </c>
       <c r="L4" t="n">
-        <v>17.78</v>
+        <v>17.74</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>16.14</v>
       </c>
       <c r="L6" t="n">
-        <v>9.93</v>
+        <v>9.91</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>10.84</v>
       </c>
       <c r="L7" t="n">
-        <v>6.61</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>11.44</v>
       </c>
       <c r="L8" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>13.34</v>
       </c>
       <c r="L11" t="n">
-        <v>8.050000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>13.95</v>
       </c>
       <c r="L12" t="n">
-        <v>8.33</v>
+        <v>8.31</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.433</v>
+        <v>22.6477</v>
       </c>
       <c r="J2" t="n">
-        <v>48168.97</v>
+        <v>48629.98</v>
       </c>
       <c r="K2" t="n">
-        <v>14.69</v>
+        <v>15.79</v>
       </c>
       <c r="L2" t="n">
-        <v>8.949999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>452.213</v>
+        <v>455.937</v>
       </c>
       <c r="J3" t="n">
-        <v>77810.03</v>
+        <v>78450.8</v>
       </c>
       <c r="K3" t="n">
-        <v>159.37</v>
+        <v>161.5</v>
       </c>
       <c r="L3" t="n">
-        <v>13.87</v>
+        <v>13.88</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5741</v>
+        <v>12.7773</v>
       </c>
       <c r="J4" t="n">
-        <v>54768.14</v>
+        <v>55653.2</v>
       </c>
       <c r="K4" t="n">
-        <v>30.41</v>
+        <v>32.51</v>
       </c>
       <c r="L4" t="n">
-        <v>17.74</v>
+        <v>18.87</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>152.461</v>
+        <v>153.744</v>
       </c>
       <c r="J5" t="n">
-        <v>45381.54</v>
+        <v>45763.44</v>
       </c>
       <c r="K5" t="n">
-        <v>13.46</v>
+        <v>14.41</v>
       </c>
       <c r="L5" t="n">
-        <v>5.24</v>
+        <v>5.59</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4893.7136</v>
+        <v>4948.4733</v>
       </c>
       <c r="J6" t="n">
-        <v>48775.64</v>
+        <v>49321.43</v>
       </c>
       <c r="K6" t="n">
-        <v>16.14</v>
+        <v>17.44</v>
       </c>
       <c r="L6" t="n">
-        <v>9.91</v>
+        <v>10.67</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>45.6192</v>
+        <v>45.9012</v>
       </c>
       <c r="J7" t="n">
-        <v>46550.74</v>
+        <v>46838.5</v>
       </c>
       <c r="K7" t="n">
-        <v>10.84</v>
+        <v>11.53</v>
       </c>
       <c r="L7" t="n">
-        <v>6.6</v>
+        <v>6.99</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.6985</v>
+        <v>16.8137</v>
       </c>
       <c r="J8" t="n">
-        <v>46801.12</v>
+        <v>47123.99</v>
       </c>
       <c r="K8" t="n">
-        <v>11.44</v>
+        <v>12.21</v>
       </c>
       <c r="L8" t="n">
-        <v>7.09</v>
+        <v>7.54</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>166.164</v>
+        <v>167.218</v>
       </c>
       <c r="J9" t="n">
-        <v>42896.57</v>
+        <v>43168.66</v>
       </c>
       <c r="K9" t="n">
-        <v>2.14</v>
+        <v>2.79</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,16 +11352,16 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1355.492</v>
+        <v>1367.675</v>
       </c>
       <c r="J10" t="n">
-        <v>19241.21</v>
+        <v>19414.15</v>
       </c>
       <c r="K10" t="n">
-        <v>277.9</v>
+        <v>281.3</v>
       </c>
       <c r="L10" t="n">
-        <v>17.78</v>
+        <v>17.79</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.686</v>
+        <v>11.813</v>
       </c>
       <c r="J11" t="n">
-        <v>47599.2</v>
+        <v>48116.5</v>
       </c>
       <c r="K11" t="n">
-        <v>13.34</v>
+        <v>14.57</v>
       </c>
       <c r="L11" t="n">
-        <v>8.039999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.3001</v>
+        <v>27.4763</v>
       </c>
       <c r="J12" t="n">
-        <v>47855.19</v>
+        <v>48164.06</v>
       </c>
       <c r="K12" t="n">
-        <v>13.95</v>
+        <v>14.68</v>
       </c>
       <c r="L12" t="n">
-        <v>8.31</v>
+        <v>8.73</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.6477</v>
+        <v>22.5977</v>
       </c>
       <c r="J2" t="n">
-        <v>48629.98</v>
+        <v>48522.62</v>
       </c>
       <c r="K2" t="n">
-        <v>15.79</v>
+        <v>15.54</v>
       </c>
       <c r="L2" t="n">
-        <v>9.58</v>
+        <v>9.41</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>455.937</v>
+        <v>456.958</v>
       </c>
       <c r="J3" t="n">
-        <v>78450.8</v>
+        <v>78626.48</v>
       </c>
       <c r="K3" t="n">
-        <v>161.5</v>
+        <v>162.09</v>
       </c>
       <c r="L3" t="n">
-        <v>13.88</v>
+        <v>13.89</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.7773</v>
+        <v>12.7608</v>
       </c>
       <c r="J4" t="n">
-        <v>55653.2</v>
+        <v>55581.34</v>
       </c>
       <c r="K4" t="n">
-        <v>32.51</v>
+        <v>32.34</v>
       </c>
       <c r="L4" t="n">
-        <v>18.87</v>
+        <v>18.75</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>153.744</v>
+        <v>153.91</v>
       </c>
       <c r="J5" t="n">
-        <v>45763.44</v>
+        <v>45812.85</v>
       </c>
       <c r="K5" t="n">
-        <v>14.41</v>
+        <v>14.54</v>
       </c>
       <c r="L5" t="n">
-        <v>5.59</v>
+        <v>5.63</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4948.4733</v>
+        <v>4945.9224</v>
       </c>
       <c r="J6" t="n">
-        <v>49321.43</v>
+        <v>49296.01</v>
       </c>
       <c r="K6" t="n">
-        <v>17.44</v>
+        <v>17.38</v>
       </c>
       <c r="L6" t="n">
-        <v>10.67</v>
+        <v>10.61</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>45.9012</v>
+        <v>45.4051</v>
       </c>
       <c r="J7" t="n">
-        <v>46838.5</v>
+        <v>46332.27</v>
       </c>
       <c r="K7" t="n">
-        <v>11.53</v>
+        <v>10.32</v>
       </c>
       <c r="L7" t="n">
-        <v>6.99</v>
+        <v>6.27</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.8137</v>
+        <v>16.7524</v>
       </c>
       <c r="J8" t="n">
-        <v>47123.99</v>
+        <v>46952.19</v>
       </c>
       <c r="K8" t="n">
-        <v>12.21</v>
+        <v>11.8</v>
       </c>
       <c r="L8" t="n">
-        <v>7.54</v>
+        <v>7.28</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>167.218</v>
+        <v>167.186</v>
       </c>
       <c r="J9" t="n">
-        <v>43168.66</v>
+        <v>43160.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="L9" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1367.675</v>
+        <v>1369.604</v>
       </c>
       <c r="J10" t="n">
-        <v>19414.15</v>
+        <v>19441.53</v>
       </c>
       <c r="K10" t="n">
-        <v>281.3</v>
+        <v>281.84</v>
       </c>
       <c r="L10" t="n">
         <v>17.79</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.813</v>
+        <v>11.743</v>
       </c>
       <c r="J11" t="n">
-        <v>48116.5</v>
+        <v>47831.38</v>
       </c>
       <c r="K11" t="n">
-        <v>14.57</v>
+        <v>13.89</v>
       </c>
       <c r="L11" t="n">
-        <v>8.75</v>
+        <v>8.34</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.4763</v>
+        <v>27.3433</v>
       </c>
       <c r="J12" t="n">
-        <v>48164.06</v>
+        <v>47930.92</v>
       </c>
       <c r="K12" t="n">
-        <v>14.68</v>
+        <v>14.13</v>
       </c>
       <c r="L12" t="n">
-        <v>8.73</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.5977</v>
+        <v>22.8377</v>
       </c>
       <c r="J2" t="n">
-        <v>48522.62</v>
+        <v>49037.95</v>
       </c>
       <c r="K2" t="n">
-        <v>15.54</v>
+        <v>16.76</v>
       </c>
       <c r="L2" t="n">
-        <v>9.41</v>
+        <v>10.12</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>456.958</v>
+        <v>460.797</v>
       </c>
       <c r="J3" t="n">
-        <v>78626.48</v>
+        <v>79287.03999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>162.09</v>
+        <v>164.29</v>
       </c>
       <c r="L3" t="n">
-        <v>13.89</v>
+        <v>13.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.7608</v>
+        <v>12.8022</v>
       </c>
       <c r="J4" t="n">
-        <v>55581.34</v>
+        <v>55761.66</v>
       </c>
       <c r="K4" t="n">
-        <v>32.34</v>
+        <v>32.77</v>
       </c>
       <c r="L4" t="n">
-        <v>18.75</v>
+        <v>18.95</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>153.91</v>
+        <v>155.659</v>
       </c>
       <c r="J5" t="n">
-        <v>45812.85</v>
+        <v>46333.46</v>
       </c>
       <c r="K5" t="n">
-        <v>14.54</v>
+        <v>15.84</v>
       </c>
       <c r="L5" t="n">
-        <v>5.63</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4945.9224</v>
+        <v>4979.4673</v>
       </c>
       <c r="J6" t="n">
-        <v>49296.01</v>
+        <v>49630.35</v>
       </c>
       <c r="K6" t="n">
-        <v>17.38</v>
+        <v>18.17</v>
       </c>
       <c r="L6" t="n">
-        <v>10.61</v>
+        <v>11.06</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>45.4051</v>
+        <v>45.58</v>
       </c>
       <c r="J7" t="n">
-        <v>46332.27</v>
+        <v>46510.74</v>
       </c>
       <c r="K7" t="n">
-        <v>10.32</v>
+        <v>10.75</v>
       </c>
       <c r="L7" t="n">
-        <v>6.27</v>
+        <v>6.51</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.7524</v>
+        <v>16.9178</v>
       </c>
       <c r="J8" t="n">
-        <v>46952.19</v>
+        <v>47415.75</v>
       </c>
       <c r="K8" t="n">
-        <v>11.8</v>
+        <v>12.9</v>
       </c>
       <c r="L8" t="n">
-        <v>7.28</v>
+        <v>7.93</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>167.186</v>
+        <v>169.356</v>
       </c>
       <c r="J9" t="n">
-        <v>43160.4</v>
+        <v>43720.61</v>
       </c>
       <c r="K9" t="n">
-        <v>2.77</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.71</v>
+        <v>2.52</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1369.604</v>
+        <v>1383.796</v>
       </c>
       <c r="J10" t="n">
-        <v>19441.53</v>
+        <v>19642.98</v>
       </c>
       <c r="K10" t="n">
-        <v>281.84</v>
+        <v>285.8</v>
       </c>
       <c r="L10" t="n">
         <v>17.79</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.743</v>
+        <v>11.909</v>
       </c>
       <c r="J11" t="n">
-        <v>47831.38</v>
+        <v>48507.52</v>
       </c>
       <c r="K11" t="n">
-        <v>13.89</v>
+        <v>15.5</v>
       </c>
       <c r="L11" t="n">
-        <v>8.34</v>
+        <v>9.26</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.3433</v>
+        <v>27.499</v>
       </c>
       <c r="J12" t="n">
-        <v>47930.92</v>
+        <v>48203.85</v>
       </c>
       <c r="K12" t="n">
-        <v>14.13</v>
+        <v>14.78</v>
       </c>
       <c r="L12" t="n">
-        <v>8.390000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.8377</v>
+        <v>22.7062</v>
       </c>
       <c r="J2" t="n">
-        <v>49037.95</v>
+        <v>48755.59</v>
       </c>
       <c r="K2" t="n">
-        <v>16.76</v>
+        <v>16.09</v>
       </c>
       <c r="L2" t="n">
-        <v>10.12</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,13 +10967,13 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>460.797</v>
+        <v>461.724</v>
       </c>
       <c r="J3" t="n">
-        <v>79287.03999999999</v>
+        <v>79446.53999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>164.29</v>
+        <v>164.82</v>
       </c>
       <c r="L3" t="n">
         <v>13.9</v>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.8022</v>
+        <v>12.937</v>
       </c>
       <c r="J4" t="n">
-        <v>55761.66</v>
+        <v>56348.8</v>
       </c>
       <c r="K4" t="n">
-        <v>32.77</v>
+        <v>34.17</v>
       </c>
       <c r="L4" t="n">
-        <v>18.95</v>
+        <v>19.68</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>155.659</v>
+        <v>155.791</v>
       </c>
       <c r="J5" t="n">
-        <v>46333.46</v>
+        <v>46372.75</v>
       </c>
       <c r="K5" t="n">
-        <v>15.84</v>
+        <v>15.94</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1</v>
+        <v>6.13</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4979.4673</v>
+        <v>4971.4322</v>
       </c>
       <c r="J6" t="n">
-        <v>49630.35</v>
+        <v>49550.26</v>
       </c>
       <c r="K6" t="n">
-        <v>18.17</v>
+        <v>17.98</v>
       </c>
       <c r="L6" t="n">
-        <v>11.06</v>
+        <v>10.93</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>45.58</v>
+        <v>45.4075</v>
       </c>
       <c r="J7" t="n">
-        <v>46510.74</v>
+        <v>46334.72</v>
       </c>
       <c r="K7" t="n">
-        <v>10.75</v>
+        <v>10.33</v>
       </c>
       <c r="L7" t="n">
-        <v>6.51</v>
+        <v>6.25</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.9178</v>
+        <v>16.8657</v>
       </c>
       <c r="J8" t="n">
-        <v>47415.75</v>
+        <v>47269.73</v>
       </c>
       <c r="K8" t="n">
-        <v>12.9</v>
+        <v>12.55</v>
       </c>
       <c r="L8" t="n">
-        <v>7.93</v>
+        <v>7.71</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>169.356</v>
+        <v>169.502</v>
       </c>
       <c r="J9" t="n">
-        <v>43720.61</v>
+        <v>43758.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>4.19</v>
       </c>
       <c r="L9" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1383.796</v>
+        <v>1386.435</v>
       </c>
       <c r="J10" t="n">
-        <v>19642.98</v>
+        <v>19680.44</v>
       </c>
       <c r="K10" t="n">
-        <v>285.8</v>
+        <v>286.53</v>
       </c>
       <c r="L10" t="n">
         <v>17.79</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.909</v>
+        <v>11.925</v>
       </c>
       <c r="J11" t="n">
-        <v>48507.52</v>
+        <v>48572.7</v>
       </c>
       <c r="K11" t="n">
-        <v>15.5</v>
+        <v>15.66</v>
       </c>
       <c r="L11" t="n">
-        <v>9.26</v>
+        <v>9.33</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.499</v>
+        <v>27.5553</v>
       </c>
       <c r="J12" t="n">
-        <v>48203.85</v>
+        <v>48302.54</v>
       </c>
       <c r="K12" t="n">
-        <v>14.78</v>
+        <v>15.01</v>
       </c>
       <c r="L12" t="n">
-        <v>8.75</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.7062</v>
+        <v>22.8487</v>
       </c>
       <c r="J2" t="n">
-        <v>48755.59</v>
+        <v>49061.57</v>
       </c>
       <c r="K2" t="n">
-        <v>16.09</v>
+        <v>16.82</v>
       </c>
       <c r="L2" t="n">
-        <v>9.710000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>461.724</v>
+        <v>463.475</v>
       </c>
       <c r="J3" t="n">
-        <v>79446.53999999999</v>
+        <v>79747.83</v>
       </c>
       <c r="K3" t="n">
-        <v>164.82</v>
+        <v>165.83</v>
       </c>
       <c r="L3" t="n">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.937</v>
+        <v>13.1646</v>
       </c>
       <c r="J4" t="n">
-        <v>56348.8</v>
+        <v>57340.14</v>
       </c>
       <c r="K4" t="n">
-        <v>34.17</v>
+        <v>36.53</v>
       </c>
       <c r="L4" t="n">
-        <v>19.68</v>
+        <v>20.92</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>155.791</v>
+        <v>155.975</v>
       </c>
       <c r="J5" t="n">
-        <v>46372.75</v>
+        <v>46427.52</v>
       </c>
       <c r="K5" t="n">
-        <v>15.94</v>
+        <v>16.07</v>
       </c>
       <c r="L5" t="n">
-        <v>6.13</v>
+        <v>6.18</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4971.4322</v>
+        <v>4987.0854</v>
       </c>
       <c r="J6" t="n">
-        <v>49550.26</v>
+        <v>49706.28</v>
       </c>
       <c r="K6" t="n">
-        <v>17.98</v>
+        <v>18.35</v>
       </c>
       <c r="L6" t="n">
-        <v>10.93</v>
+        <v>11.13</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>45.4075</v>
+        <v>45.6592</v>
       </c>
       <c r="J7" t="n">
-        <v>46334.72</v>
+        <v>46591.56</v>
       </c>
       <c r="K7" t="n">
-        <v>10.33</v>
+        <v>10.94</v>
       </c>
       <c r="L7" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.8657</v>
+        <v>16.942</v>
       </c>
       <c r="J8" t="n">
-        <v>47269.73</v>
+        <v>47483.58</v>
       </c>
       <c r="K8" t="n">
-        <v>12.55</v>
+        <v>13.06</v>
       </c>
       <c r="L8" t="n">
-        <v>7.71</v>
+        <v>8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,13 +11297,13 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>169.502</v>
+        <v>169.491</v>
       </c>
       <c r="J9" t="n">
-        <v>43758.3</v>
+        <v>43755.46</v>
       </c>
       <c r="K9" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="L9" t="n">
         <v>2.57</v>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1386.435</v>
+        <v>1389.441</v>
       </c>
       <c r="J10" t="n">
-        <v>19680.44</v>
+        <v>19723.11</v>
       </c>
       <c r="K10" t="n">
-        <v>286.53</v>
+        <v>287.37</v>
       </c>
       <c r="L10" t="n">
         <v>17.79</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>11.925</v>
+        <v>12.07</v>
       </c>
       <c r="J11" t="n">
-        <v>48572.7</v>
+        <v>49163.31</v>
       </c>
       <c r="K11" t="n">
-        <v>15.66</v>
+        <v>17.06</v>
       </c>
       <c r="L11" t="n">
-        <v>9.33</v>
+        <v>10.13</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.5553</v>
+        <v>27.7504</v>
       </c>
       <c r="J12" t="n">
-        <v>48302.54</v>
+        <v>48644.54</v>
       </c>
       <c r="K12" t="n">
-        <v>15.01</v>
+        <v>15.83</v>
       </c>
       <c r="L12" t="n">
-        <v>8.869999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10921,7 +10921,7 @@
         <v>16.82</v>
       </c>
       <c r="L2" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>36.53</v>
       </c>
       <c r="L4" t="n">
-        <v>20.92</v>
+        <v>20.88</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>16.07</v>
       </c>
       <c r="L5" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>18.35</v>
       </c>
       <c r="L6" t="n">
-        <v>11.13</v>
+        <v>11.11</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>10.94</v>
       </c>
       <c r="L7" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>13.06</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>4.18</v>
       </c>
       <c r="L9" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>17.06</v>
       </c>
       <c r="L11" t="n">
-        <v>10.13</v>
+        <v>10.11</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>15.83</v>
       </c>
       <c r="L12" t="n">
-        <v>9.32</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10921,7 +10921,7 @@
         <v>16.82</v>
       </c>
       <c r="L2" t="n">
-        <v>10.1</v>
+        <v>10.08</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>36.53</v>
       </c>
       <c r="L4" t="n">
-        <v>20.88</v>
+        <v>20.84</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>16.07</v>
       </c>
       <c r="L5" t="n">
-        <v>6.17</v>
+        <v>6.16</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>18.35</v>
       </c>
       <c r="L6" t="n">
-        <v>11.11</v>
+        <v>11.09</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>10.94</v>
       </c>
       <c r="L7" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>13.06</v>
       </c>
       <c r="L8" t="n">
-        <v>7.99</v>
+        <v>7.97</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>17.06</v>
       </c>
       <c r="L11" t="n">
-        <v>10.11</v>
+        <v>10.09</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>15.83</v>
       </c>
       <c r="L12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.8487</v>
+        <v>23.0912</v>
       </c>
       <c r="J2" t="n">
-        <v>49061.57</v>
+        <v>49582.28</v>
       </c>
       <c r="K2" t="n">
-        <v>16.82</v>
+        <v>18.06</v>
       </c>
       <c r="L2" t="n">
-        <v>10.08</v>
+        <v>10.78</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>463.475</v>
+        <v>470.419</v>
       </c>
       <c r="J3" t="n">
-        <v>79747.83</v>
+        <v>80942.64999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>165.83</v>
+        <v>169.81</v>
       </c>
       <c r="L3" t="n">
-        <v>13.91</v>
+        <v>13.94</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>13.1646</v>
+        <v>13.4013</v>
       </c>
       <c r="J4" t="n">
-        <v>57340.14</v>
+        <v>58371.12</v>
       </c>
       <c r="K4" t="n">
-        <v>36.53</v>
+        <v>38.99</v>
       </c>
       <c r="L4" t="n">
-        <v>20.84</v>
+        <v>22.11</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>155.975</v>
+        <v>158.563</v>
       </c>
       <c r="J5" t="n">
-        <v>46427.52</v>
+        <v>47197.86</v>
       </c>
       <c r="K5" t="n">
-        <v>16.07</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>6.16</v>
+        <v>6.86</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4987.0854</v>
+        <v>5055.2385</v>
       </c>
       <c r="J6" t="n">
-        <v>49706.28</v>
+        <v>50385.56</v>
       </c>
       <c r="K6" t="n">
-        <v>18.35</v>
+        <v>19.97</v>
       </c>
       <c r="L6" t="n">
-        <v>11.09</v>
+        <v>12.01</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>45.6592</v>
+        <v>46.2628</v>
       </c>
       <c r="J7" t="n">
-        <v>46591.56</v>
+        <v>47207.49</v>
       </c>
       <c r="K7" t="n">
-        <v>10.94</v>
+        <v>12.4</v>
       </c>
       <c r="L7" t="n">
-        <v>6.58</v>
+        <v>7.42</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>16.942</v>
+        <v>17.226</v>
       </c>
       <c r="J8" t="n">
-        <v>47483.58</v>
+        <v>48279.55</v>
       </c>
       <c r="K8" t="n">
-        <v>13.06</v>
+        <v>14.96</v>
       </c>
       <c r="L8" t="n">
-        <v>7.97</v>
+        <v>9.08</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>169.491</v>
+        <v>172.286</v>
       </c>
       <c r="J9" t="n">
-        <v>43755.46</v>
+        <v>44477.01</v>
       </c>
       <c r="K9" t="n">
-        <v>4.18</v>
+        <v>5.9</v>
       </c>
       <c r="L9" t="n">
-        <v>2.56</v>
+        <v>3.59</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,16 +11352,16 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1389.441</v>
+        <v>1410.547</v>
       </c>
       <c r="J10" t="n">
-        <v>19723.11</v>
+        <v>20022.71</v>
       </c>
       <c r="K10" t="n">
-        <v>287.37</v>
+        <v>293.25</v>
       </c>
       <c r="L10" t="n">
-        <v>17.79</v>
+        <v>17.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>12.07</v>
+        <v>12.253</v>
       </c>
       <c r="J11" t="n">
-        <v>49163.31</v>
+        <v>49908.7</v>
       </c>
       <c r="K11" t="n">
-        <v>17.06</v>
+        <v>18.84</v>
       </c>
       <c r="L11" t="n">
-        <v>10.09</v>
+        <v>11.09</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.7504</v>
+        <v>27.8757</v>
       </c>
       <c r="J12" t="n">
-        <v>48644.54</v>
+        <v>48864.18</v>
       </c>
       <c r="K12" t="n">
-        <v>15.83</v>
+        <v>16.35</v>
       </c>
       <c r="L12" t="n">
-        <v>9.289999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>23.0912</v>
+        <v>23.0866</v>
       </c>
       <c r="J2" t="n">
-        <v>49582.28</v>
+        <v>49572.4</v>
       </c>
       <c r="K2" t="n">
-        <v>18.06</v>
+        <v>18.04</v>
       </c>
       <c r="L2" t="n">
-        <v>10.78</v>
+        <v>10.75</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,16 +10967,16 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>470.419</v>
+        <v>466.807</v>
       </c>
       <c r="J3" t="n">
-        <v>80942.64999999999</v>
+        <v>80321.14999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>169.81</v>
+        <v>167.74</v>
       </c>
       <c r="L3" t="n">
-        <v>13.94</v>
+        <v>13.92</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>13.4013</v>
+        <v>13.4349</v>
       </c>
       <c r="J4" t="n">
-        <v>58371.12</v>
+        <v>58517.47</v>
       </c>
       <c r="K4" t="n">
-        <v>38.99</v>
+        <v>39.33</v>
       </c>
       <c r="L4" t="n">
-        <v>22.11</v>
+        <v>22.26</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>158.563</v>
+        <v>157.728</v>
       </c>
       <c r="J5" t="n">
-        <v>47197.86</v>
+        <v>46949.32</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>17.38</v>
       </c>
       <c r="L5" t="n">
-        <v>6.86</v>
+        <v>6.62</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5055.2385</v>
+        <v>5031.9183</v>
       </c>
       <c r="J6" t="n">
-        <v>50385.56</v>
+        <v>50153.13</v>
       </c>
       <c r="K6" t="n">
-        <v>19.97</v>
+        <v>19.42</v>
       </c>
       <c r="L6" t="n">
-        <v>12.01</v>
+        <v>11.67</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.2628</v>
+        <v>45.9213</v>
       </c>
       <c r="J7" t="n">
-        <v>47207.49</v>
+        <v>46859.01</v>
       </c>
       <c r="K7" t="n">
-        <v>12.4</v>
+        <v>11.57</v>
       </c>
       <c r="L7" t="n">
-        <v>7.42</v>
+        <v>6.93</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>17.226</v>
+        <v>17.1026</v>
       </c>
       <c r="J8" t="n">
-        <v>48279.55</v>
+        <v>47933.7</v>
       </c>
       <c r="K8" t="n">
-        <v>14.96</v>
+        <v>14.13</v>
       </c>
       <c r="L8" t="n">
-        <v>9.08</v>
+        <v>8.58</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>172.286</v>
+        <v>171.483</v>
       </c>
       <c r="J9" t="n">
-        <v>44477.01</v>
+        <v>44269.71</v>
       </c>
       <c r="K9" t="n">
-        <v>5.9</v>
+        <v>5.41</v>
       </c>
       <c r="L9" t="n">
-        <v>3.59</v>
+        <v>3.29</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1410.547</v>
+        <v>1402.659</v>
       </c>
       <c r="J10" t="n">
-        <v>20022.71</v>
+        <v>19910.74</v>
       </c>
       <c r="K10" t="n">
-        <v>293.25</v>
+        <v>291.05</v>
       </c>
       <c r="L10" t="n">
         <v>17.8</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>12.253</v>
+        <v>12.217</v>
       </c>
       <c r="J11" t="n">
-        <v>49908.7</v>
+        <v>49762.06</v>
       </c>
       <c r="K11" t="n">
-        <v>18.84</v>
+        <v>18.49</v>
       </c>
       <c r="L11" t="n">
-        <v>11.09</v>
+        <v>10.87</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.8757</v>
+        <v>27.9206</v>
       </c>
       <c r="J12" t="n">
-        <v>48864.18</v>
+        <v>48942.89</v>
       </c>
       <c r="K12" t="n">
-        <v>16.35</v>
+        <v>16.54</v>
       </c>
       <c r="L12" t="n">
-        <v>9.57</v>
+        <v>9.66</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>23.0866</v>
+        <v>23.1825</v>
       </c>
       <c r="J2" t="n">
-        <v>49572.4</v>
+        <v>49778.32</v>
       </c>
       <c r="K2" t="n">
-        <v>18.04</v>
+        <v>18.53</v>
       </c>
       <c r="L2" t="n">
-        <v>10.75</v>
+        <v>11.01</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,13 +10967,13 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>466.807</v>
+        <v>467.492</v>
       </c>
       <c r="J3" t="n">
-        <v>80321.14999999999</v>
+        <v>80439.00999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>167.74</v>
+        <v>168.13</v>
       </c>
       <c r="L3" t="n">
         <v>13.92</v>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>13.4349</v>
+        <v>13.7043</v>
       </c>
       <c r="J4" t="n">
-        <v>58517.47</v>
+        <v>59690.87</v>
       </c>
       <c r="K4" t="n">
-        <v>39.33</v>
+        <v>42.13</v>
       </c>
       <c r="L4" t="n">
-        <v>22.26</v>
+        <v>23.69</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>157.728</v>
+        <v>157.674</v>
       </c>
       <c r="J5" t="n">
-        <v>46949.32</v>
+        <v>46933.24</v>
       </c>
       <c r="K5" t="n">
-        <v>17.38</v>
+        <v>17.34</v>
       </c>
       <c r="L5" t="n">
-        <v>6.62</v>
+        <v>6.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5031.9183</v>
+        <v>5042.1738</v>
       </c>
       <c r="J6" t="n">
-        <v>50153.13</v>
+        <v>50255.35</v>
       </c>
       <c r="K6" t="n">
-        <v>19.42</v>
+        <v>19.66</v>
       </c>
       <c r="L6" t="n">
-        <v>11.67</v>
+        <v>11.79</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>45.9213</v>
+        <v>46.1109</v>
       </c>
       <c r="J7" t="n">
-        <v>46859.01</v>
+        <v>47052.48</v>
       </c>
       <c r="K7" t="n">
-        <v>11.57</v>
+        <v>12.04</v>
       </c>
       <c r="L7" t="n">
-        <v>6.93</v>
+        <v>7.18</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>17.1026</v>
+        <v>17.178</v>
       </c>
       <c r="J8" t="n">
-        <v>47933.7</v>
+        <v>48145.02</v>
       </c>
       <c r="K8" t="n">
-        <v>14.13</v>
+        <v>14.64</v>
       </c>
       <c r="L8" t="n">
-        <v>8.58</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>171.483</v>
+        <v>171.904</v>
       </c>
       <c r="J9" t="n">
-        <v>44269.71</v>
+        <v>44378.39</v>
       </c>
       <c r="K9" t="n">
-        <v>5.41</v>
+        <v>5.67</v>
       </c>
       <c r="L9" t="n">
-        <v>3.29</v>
+        <v>3.44</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1402.659</v>
+        <v>1405.212</v>
       </c>
       <c r="J10" t="n">
-        <v>19910.74</v>
+        <v>19946.98</v>
       </c>
       <c r="K10" t="n">
-        <v>291.05</v>
+        <v>291.77</v>
       </c>
       <c r="L10" t="n">
         <v>17.8</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>12.217</v>
+        <v>12.292</v>
       </c>
       <c r="J11" t="n">
-        <v>49762.06</v>
+        <v>50067.55</v>
       </c>
       <c r="K11" t="n">
-        <v>18.49</v>
+        <v>19.21</v>
       </c>
       <c r="L11" t="n">
-        <v>10.87</v>
+        <v>11.26</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>27.9206</v>
+        <v>28.0592</v>
       </c>
       <c r="J12" t="n">
-        <v>48942.89</v>
+        <v>49185.84</v>
       </c>
       <c r="K12" t="n">
-        <v>16.54</v>
+        <v>17.12</v>
       </c>
       <c r="L12" t="n">
-        <v>9.66</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>23.1825</v>
+        <v>23.2385</v>
       </c>
       <c r="J2" t="n">
-        <v>49778.32</v>
+        <v>49898.57</v>
       </c>
       <c r="K2" t="n">
-        <v>18.53</v>
+        <v>18.81</v>
       </c>
       <c r="L2" t="n">
-        <v>11.01</v>
+        <v>11.15</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,13 +10967,13 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>467.492</v>
+        <v>466.599</v>
       </c>
       <c r="J3" t="n">
-        <v>80439.00999999999</v>
+        <v>80285.36</v>
       </c>
       <c r="K3" t="n">
-        <v>168.13</v>
+        <v>167.62</v>
       </c>
       <c r="L3" t="n">
         <v>13.92</v>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>13.7043</v>
+        <v>13.6673</v>
       </c>
       <c r="J4" t="n">
-        <v>59690.87</v>
+        <v>59529.72</v>
       </c>
       <c r="K4" t="n">
-        <v>42.13</v>
+        <v>41.74</v>
       </c>
       <c r="L4" t="n">
-        <v>23.69</v>
+        <v>23.45</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>157.674</v>
+        <v>157.591</v>
       </c>
       <c r="J5" t="n">
-        <v>46933.24</v>
+        <v>46908.54</v>
       </c>
       <c r="K5" t="n">
-        <v>17.34</v>
+        <v>17.28</v>
       </c>
       <c r="L5" t="n">
-        <v>6.6</v>
+        <v>6.57</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5042.1738</v>
+        <v>5035.8925</v>
       </c>
       <c r="J6" t="n">
-        <v>50255.35</v>
+        <v>50192.74</v>
       </c>
       <c r="K6" t="n">
-        <v>19.66</v>
+        <v>19.51</v>
       </c>
       <c r="L6" t="n">
-        <v>11.79</v>
+        <v>11.68</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.1109</v>
+        <v>45.9665</v>
       </c>
       <c r="J7" t="n">
-        <v>47052.48</v>
+        <v>46905.14</v>
       </c>
       <c r="K7" t="n">
-        <v>12.04</v>
+        <v>11.68</v>
       </c>
       <c r="L7" t="n">
-        <v>7.18</v>
+        <v>6.97</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>17.178</v>
+        <v>17.127</v>
       </c>
       <c r="J8" t="n">
-        <v>48145.02</v>
+        <v>48002.08</v>
       </c>
       <c r="K8" t="n">
-        <v>14.64</v>
+        <v>14.3</v>
       </c>
       <c r="L8" t="n">
-        <v>8.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>171.904</v>
+        <v>171.72</v>
       </c>
       <c r="J9" t="n">
-        <v>44378.39</v>
+        <v>44330.89</v>
       </c>
       <c r="K9" t="n">
-        <v>5.67</v>
+        <v>5.56</v>
       </c>
       <c r="L9" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1405.212</v>
+        <v>1402.97</v>
       </c>
       <c r="J10" t="n">
-        <v>19946.98</v>
+        <v>19915.16</v>
       </c>
       <c r="K10" t="n">
-        <v>291.77</v>
+        <v>291.14</v>
       </c>
       <c r="L10" t="n">
         <v>17.8</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>12.292</v>
+        <v>12.336</v>
       </c>
       <c r="J11" t="n">
-        <v>50067.55</v>
+        <v>50246.77</v>
       </c>
       <c r="K11" t="n">
-        <v>19.21</v>
+        <v>19.64</v>
       </c>
       <c r="L11" t="n">
-        <v>11.26</v>
+        <v>11.48</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>28.0592</v>
+        <v>28.1365</v>
       </c>
       <c r="J12" t="n">
-        <v>49185.84</v>
+        <v>49321.34</v>
       </c>
       <c r="K12" t="n">
-        <v>17.12</v>
+        <v>17.44</v>
       </c>
       <c r="L12" t="n">
-        <v>9.970000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -10912,16 +10912,16 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>23.2385</v>
+        <v>23.2719</v>
       </c>
       <c r="J2" t="n">
-        <v>49898.57</v>
+        <v>49970.28</v>
       </c>
       <c r="K2" t="n">
-        <v>18.81</v>
+        <v>18.98</v>
       </c>
       <c r="L2" t="n">
-        <v>11.15</v>
+        <v>11.23</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -10967,13 +10967,13 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>466.599</v>
+        <v>465.703</v>
       </c>
       <c r="J3" t="n">
-        <v>80285.36</v>
+        <v>80131.19</v>
       </c>
       <c r="K3" t="n">
-        <v>167.62</v>
+        <v>167.1</v>
       </c>
       <c r="L3" t="n">
         <v>13.92</v>
@@ -11022,16 +11022,16 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>13.6673</v>
+        <v>13.8506</v>
       </c>
       <c r="J4" t="n">
-        <v>59529.72</v>
+        <v>60328.1</v>
       </c>
       <c r="K4" t="n">
-        <v>41.74</v>
+        <v>43.65</v>
       </c>
       <c r="L4" t="n">
-        <v>23.45</v>
+        <v>24.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11077,16 +11077,16 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>157.591</v>
+        <v>157.47</v>
       </c>
       <c r="J5" t="n">
-        <v>46908.54</v>
+        <v>46872.52</v>
       </c>
       <c r="K5" t="n">
-        <v>17.28</v>
+        <v>17.19</v>
       </c>
       <c r="L5" t="n">
-        <v>6.57</v>
+        <v>6.53</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5035.8925</v>
+        <v>5049.2657</v>
       </c>
       <c r="J6" t="n">
-        <v>50192.74</v>
+        <v>50326.03</v>
       </c>
       <c r="K6" t="n">
-        <v>19.51</v>
+        <v>19.83</v>
       </c>
       <c r="L6" t="n">
-        <v>11.68</v>
+        <v>11.84</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11187,16 +11187,16 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>45.9665</v>
+        <v>46.2448</v>
       </c>
       <c r="J7" t="n">
-        <v>46905.14</v>
+        <v>47189.12</v>
       </c>
       <c r="K7" t="n">
-        <v>11.68</v>
+        <v>12.36</v>
       </c>
       <c r="L7" t="n">
-        <v>6.97</v>
+        <v>7.35</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>17.127</v>
+        <v>17.157</v>
       </c>
       <c r="J8" t="n">
-        <v>48002.08</v>
+        <v>48086.16</v>
       </c>
       <c r="K8" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="L8" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -11297,16 +11297,16 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>171.72</v>
+        <v>171.599</v>
       </c>
       <c r="J9" t="n">
-        <v>44330.89</v>
+        <v>44299.65</v>
       </c>
       <c r="K9" t="n">
-        <v>5.56</v>
+        <v>5.48</v>
       </c>
       <c r="L9" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1402.97</v>
+        <v>1400.293</v>
       </c>
       <c r="J10" t="n">
-        <v>19915.16</v>
+        <v>19877.16</v>
       </c>
       <c r="K10" t="n">
-        <v>291.14</v>
+        <v>290.39</v>
       </c>
       <c r="L10" t="n">
         <v>17.8</v>
@@ -11407,16 +11407,16 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>12.336</v>
+        <v>12.384</v>
       </c>
       <c r="J11" t="n">
-        <v>50246.77</v>
+        <v>50442.29</v>
       </c>
       <c r="K11" t="n">
-        <v>19.64</v>
+        <v>20.11</v>
       </c>
       <c r="L11" t="n">
-        <v>11.48</v>
+        <v>11.73</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -11462,16 +11462,16 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>28.1365</v>
+        <v>28.1984</v>
       </c>
       <c r="J12" t="n">
-        <v>49321.34</v>
+        <v>49429.85</v>
       </c>
       <c r="K12" t="n">
-        <v>17.44</v>
+        <v>17.7</v>
       </c>
       <c r="L12" t="n">
-        <v>10.13</v>
+        <v>10.26</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -515,10 +515,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G2" t="n">
+        <v>101635</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -576,10 +574,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G3" t="n">
+        <v>101635</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -637,10 +633,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G4" t="n">
+        <v>101979</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -698,10 +692,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G5" t="n">
+        <v>101635</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -759,10 +751,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G6" t="n">
+        <v>101979</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -820,10 +810,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G7" t="n">
+        <v>101635</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -881,10 +869,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G8" t="n">
+        <v>101979</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -942,10 +928,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G9" t="n">
+        <v>101635</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1003,10 +987,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G10" t="n">
+        <v>101979</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1064,10 +1046,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G11" t="n">
+        <v>101635</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1125,10 +1105,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G12" t="n">
+        <v>101979</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1186,10 +1164,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G13" t="n">
+        <v>101635</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1247,10 +1223,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G14" t="n">
+        <v>101979</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1308,10 +1282,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G15" t="n">
+        <v>101635</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1369,10 +1341,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G16" t="n">
+        <v>101979</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1430,10 +1400,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G17" t="n">
+        <v>101635</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1491,10 +1459,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G18" t="n">
+        <v>101979</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1552,10 +1518,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G19" t="n">
+        <v>101635</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1613,10 +1577,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G20" t="n">
+        <v>101979</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1674,10 +1636,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G21" t="n">
+        <v>101635</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1735,10 +1695,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G22" t="n">
+        <v>101979</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1796,10 +1754,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G23" t="n">
+        <v>101635</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1857,10 +1813,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G24" t="n">
+        <v>101979</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1918,10 +1872,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G25" t="n">
+        <v>101635</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1979,10 +1931,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G26" t="n">
+        <v>101979</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2040,10 +1990,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G27" t="n">
+        <v>101635</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2101,10 +2049,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G28" t="n">
+        <v>101979</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2162,10 +2108,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G29" t="n">
+        <v>101635</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2223,10 +2167,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G30" t="n">
+        <v>101979</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2284,10 +2226,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G31" t="n">
+        <v>101635</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2345,10 +2285,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G32" t="n">
+        <v>101979</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2406,10 +2344,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G33" t="n">
+        <v>101635</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2467,10 +2403,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G34" t="n">
+        <v>101979</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2528,10 +2462,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G35" t="n">
+        <v>101635</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2589,10 +2521,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G36" t="n">
+        <v>101979</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2650,10 +2580,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G37" t="n">
+        <v>101635</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2711,10 +2639,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G38" t="n">
+        <v>101979</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2772,10 +2698,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G39" t="n">
+        <v>101635</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2833,10 +2757,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G40" t="n">
+        <v>101979</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2894,10 +2816,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G41" t="n">
+        <v>101635</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2955,10 +2875,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G42" t="n">
+        <v>101979</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3016,10 +2934,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G43" t="n">
+        <v>101635</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3077,10 +2993,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G44" t="n">
+        <v>101979</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3138,10 +3052,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G45" t="n">
+        <v>101635</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3199,10 +3111,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G46" t="n">
+        <v>101979</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3260,10 +3170,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G47" t="n">
+        <v>101635</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3321,10 +3229,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G48" t="n">
+        <v>101979</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3382,10 +3288,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G49" t="n">
+        <v>101635</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3443,10 +3347,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G50" t="n">
+        <v>101979</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3504,10 +3406,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G51" t="n">
+        <v>101635</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3565,10 +3465,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G52" t="n">
+        <v>101979</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3626,10 +3524,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G53" t="n">
+        <v>101635</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3687,10 +3583,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G54" t="n">
+        <v>101979</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3748,10 +3642,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G55" t="n">
+        <v>101635</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3809,10 +3701,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G56" t="n">
+        <v>101979</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3870,10 +3760,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G57" t="n">
+        <v>101635</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3931,10 +3819,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G58" t="n">
+        <v>101979</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3992,10 +3878,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G59" t="n">
+        <v>101635</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4053,10 +3937,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G60" t="n">
+        <v>101979</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4114,10 +3996,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G61" t="n">
+        <v>101635</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4175,10 +4055,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G62" t="n">
+        <v>101979</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4236,10 +4114,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G63" t="n">
+        <v>101635</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4297,10 +4173,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G64" t="n">
+        <v>101979</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4358,10 +4232,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G65" t="n">
+        <v>101635</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4419,10 +4291,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G66" t="n">
+        <v>101979</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4480,10 +4350,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G67" t="n">
+        <v>101635</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4541,10 +4409,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G68" t="n">
+        <v>101979</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -4602,10 +4468,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G69" t="n">
+        <v>101635</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4663,10 +4527,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G70" t="n">
+        <v>101979</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4724,10 +4586,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G71" t="n">
+        <v>101635</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4785,10 +4645,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G72" t="n">
+        <v>101979</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4846,10 +4704,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G73" t="n">
+        <v>101635</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4907,10 +4763,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G74" t="n">
+        <v>101979</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4968,10 +4822,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G75" t="n">
+        <v>101635</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5029,10 +4881,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G76" t="n">
+        <v>101979</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5090,10 +4940,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G77" t="n">
+        <v>101635</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5151,10 +4999,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G78" t="n">
+        <v>101635</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5212,10 +5058,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G79" t="n">
+        <v>101635</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5273,10 +5117,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G80" t="n">
+        <v>101635</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5334,10 +5176,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G81" t="n">
+        <v>101635</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5395,10 +5235,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G82" t="n">
+        <v>101635</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5456,10 +5294,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G83" t="n">
+        <v>101635</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5517,10 +5353,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G84" t="n">
+        <v>101635</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5578,10 +5412,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G85" t="n">
+        <v>101635</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5639,10 +5471,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G86" t="n">
+        <v>101635</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5700,10 +5530,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G87" t="n">
+        <v>101635</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5761,10 +5589,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G88" t="n">
+        <v>101635</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -5822,10 +5648,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G89" t="n">
+        <v>101635</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5883,10 +5707,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G90" t="n">
+        <v>101635</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -5944,10 +5766,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G91" t="n">
+        <v>101635</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6005,10 +5825,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G92" t="n">
+        <v>101635</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6066,10 +5884,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G93" t="n">
+        <v>101635</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6127,10 +5943,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G94" t="n">
+        <v>101635</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6188,10 +6002,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G95" t="n">
+        <v>101635</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6249,10 +6061,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G96" t="n">
+        <v>101635</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6310,10 +6120,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G97" t="n">
+        <v>101635</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6371,10 +6179,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G98" t="n">
+        <v>101635</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6432,10 +6238,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G99" t="n">
+        <v>101635</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6493,10 +6297,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G100" t="n">
+        <v>101635</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6554,10 +6356,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G101" t="n">
+        <v>101635</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6615,10 +6415,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G102" t="n">
+        <v>101635</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6676,10 +6474,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G103" t="n">
+        <v>101635</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6737,10 +6533,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G104" t="n">
+        <v>101635</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6798,10 +6592,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G105" t="n">
+        <v>101635</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6859,10 +6651,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G106" t="n">
+        <v>101635</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -6920,10 +6710,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G107" t="n">
+        <v>101635</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -6981,10 +6769,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G108" t="n">
+        <v>101635</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -7042,10 +6828,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G109" t="n">
+        <v>101635</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7103,10 +6887,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G110" t="n">
+        <v>101635</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -7164,10 +6946,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G111" t="n">
+        <v>101635</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7225,10 +7005,8 @@
           <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>101979</t>
-        </is>
+      <c r="G112" t="n">
+        <v>101979</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -7286,10 +7064,8 @@
           <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>101635</t>
-        </is>
+      <c r="G113" t="n">
+        <v>101635</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -7347,10 +7123,8 @@
           <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>111569</t>
-        </is>
+      <c r="G114" t="n">
+        <v>111569</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7408,10 +7182,8 @@
           <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>150518</t>
-        </is>
+      <c r="G115" t="n">
+        <v>150518</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -7469,10 +7241,8 @@
           <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>152657</t>
-        </is>
+      <c r="G116" t="n">
+        <v>152657</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7530,10 +7300,8 @@
           <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>152600</t>
-        </is>
+      <c r="G117" t="n">
+        <v>152600</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7591,10 +7359,8 @@
           <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>120833</t>
-        </is>
+      <c r="G118" t="n">
+        <v>120833</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7652,10 +7418,8 @@
           <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>118481</t>
-        </is>
+      <c r="G119" t="n">
+        <v>118481</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7713,10 +7477,8 @@
           <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>150915</t>
-        </is>
+      <c r="G120" t="n">
+        <v>150915</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7774,10 +7536,8 @@
           <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>118668</t>
-        </is>
+      <c r="G121" t="n">
+        <v>118668</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7835,10 +7595,8 @@
           <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>150440</t>
-        </is>
+      <c r="G122" t="n">
+        <v>150440</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -7896,10 +7654,8 @@
           <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>150518</t>
-        </is>
+      <c r="G123" t="n">
+        <v>150518</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -7957,10 +7713,8 @@
           <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>152657</t>
-        </is>
+      <c r="G124" t="n">
+        <v>152657</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -8018,10 +7772,8 @@
           <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>152600</t>
-        </is>
+      <c r="G125" t="n">
+        <v>152600</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -8079,10 +7831,8 @@
           <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>120833</t>
-        </is>
+      <c r="G126" t="n">
+        <v>120833</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -8140,10 +7890,8 @@
           <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>118481</t>
-        </is>
+      <c r="G127" t="n">
+        <v>118481</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -8201,10 +7949,8 @@
           <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>150915</t>
-        </is>
+      <c r="G128" t="n">
+        <v>150915</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -8262,10 +8008,8 @@
           <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>118668</t>
-        </is>
+      <c r="G129" t="n">
+        <v>118668</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -8323,10 +8067,8 @@
           <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>150440</t>
-        </is>
+      <c r="G130" t="n">
+        <v>150440</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8384,10 +8126,8 @@
           <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>150518</t>
-        </is>
+      <c r="G131" t="n">
+        <v>150518</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8445,10 +8185,8 @@
           <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>152657</t>
-        </is>
+      <c r="G132" t="n">
+        <v>152657</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8506,10 +8244,8 @@
           <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>152600</t>
-        </is>
+      <c r="G133" t="n">
+        <v>152600</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -8567,10 +8303,8 @@
           <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>120833</t>
-        </is>
+      <c r="G134" t="n">
+        <v>120833</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -8628,10 +8362,8 @@
           <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>118481</t>
-        </is>
+      <c r="G135" t="n">
+        <v>118481</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8689,10 +8421,8 @@
           <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>150915</t>
-        </is>
+      <c r="G136" t="n">
+        <v>150915</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8750,10 +8480,8 @@
           <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>118668</t>
-        </is>
+      <c r="G137" t="n">
+        <v>118668</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8811,10 +8539,8 @@
           <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>150440</t>
-        </is>
+      <c r="G138" t="n">
+        <v>150440</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -8872,10 +8598,8 @@
           <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>150518</t>
-        </is>
+      <c r="G139" t="n">
+        <v>150518</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -8933,10 +8657,8 @@
           <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>152657</t>
-        </is>
+      <c r="G140" t="n">
+        <v>152657</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -8994,10 +8716,8 @@
           <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>152600</t>
-        </is>
+      <c r="G141" t="n">
+        <v>152600</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -9055,10 +8775,8 @@
           <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>120833</t>
-        </is>
+      <c r="G142" t="n">
+        <v>120833</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -9116,10 +8834,8 @@
           <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>118481</t>
-        </is>
+      <c r="G143" t="n">
+        <v>118481</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9177,10 +8893,8 @@
           <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>150915</t>
-        </is>
+      <c r="G144" t="n">
+        <v>150915</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9238,10 +8952,8 @@
           <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>118668</t>
-        </is>
+      <c r="G145" t="n">
+        <v>118668</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -9299,10 +9011,8 @@
           <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>150440</t>
-        </is>
+      <c r="G146" t="n">
+        <v>150440</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -9360,10 +9070,8 @@
           <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>150518</t>
-        </is>
+      <c r="G147" t="n">
+        <v>150518</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9421,10 +9129,8 @@
           <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>152657</t>
-        </is>
+      <c r="G148" t="n">
+        <v>152657</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9482,10 +9188,8 @@
           <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>152600</t>
-        </is>
+      <c r="G149" t="n">
+        <v>152600</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9543,10 +9247,8 @@
           <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>120833</t>
-        </is>
+      <c r="G150" t="n">
+        <v>120833</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9604,10 +9306,8 @@
           <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>118481</t>
-        </is>
+      <c r="G151" t="n">
+        <v>118481</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9665,10 +9365,8 @@
           <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>150915</t>
-        </is>
+      <c r="G152" t="n">
+        <v>150915</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9726,10 +9424,8 @@
           <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>118668</t>
-        </is>
+      <c r="G153" t="n">
+        <v>118668</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -9787,10 +9483,8 @@
           <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>150440</t>
-        </is>
+      <c r="G154" t="n">
+        <v>150440</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -9848,10 +9542,8 @@
           <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>150518</t>
-        </is>
+      <c r="G155" t="n">
+        <v>150518</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -9909,10 +9601,8 @@
           <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>152657</t>
-        </is>
+      <c r="G156" t="n">
+        <v>152657</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -9970,10 +9660,8 @@
           <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>152600</t>
-        </is>
+      <c r="G157" t="n">
+        <v>152600</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -10031,10 +9719,8 @@
           <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>120833</t>
-        </is>
+      <c r="G158" t="n">
+        <v>120833</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -10092,10 +9778,8 @@
           <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>118481</t>
-        </is>
+      <c r="G159" t="n">
+        <v>118481</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -10153,10 +9837,8 @@
           <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>150915</t>
-        </is>
+      <c r="G160" t="n">
+        <v>150915</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -10214,10 +9896,8 @@
           <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>118668</t>
-        </is>
+      <c r="G161" t="n">
+        <v>118668</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -10275,10 +9955,8 @@
           <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>150440</t>
-        </is>
+      <c r="G162" t="n">
+        <v>150440</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -10336,10 +10014,8 @@
           <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>150518</t>
-        </is>
+      <c r="G163" t="n">
+        <v>150518</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -10397,10 +10073,8 @@
           <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>152657</t>
-        </is>
+      <c r="G164" t="n">
+        <v>152657</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -10458,10 +10132,8 @@
           <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>152600</t>
-        </is>
+      <c r="G165" t="n">
+        <v>152600</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -10519,10 +10191,8 @@
           <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>120833</t>
-        </is>
+      <c r="G166" t="n">
+        <v>120833</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -10580,10 +10250,8 @@
           <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>118481</t>
-        </is>
+      <c r="G167" t="n">
+        <v>118481</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -10641,10 +10309,8 @@
           <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>150915</t>
-        </is>
+      <c r="G168" t="n">
+        <v>150915</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -10702,10 +10368,8 @@
           <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>118668</t>
-        </is>
+      <c r="G169" t="n">
+        <v>118668</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -10763,10 +10427,8 @@
           <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>150440</t>
-        </is>
+      <c r="G170" t="n">
+        <v>150440</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -10912,20 +10574,20 @@
         <v>41997.9</v>
       </c>
       <c r="I2" t="n">
-        <v>23.2719</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>49970.28</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>18.98</v>
+        <v>-100</v>
       </c>
       <c r="L2" t="n">
-        <v>11.23</v>
+        <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>✅ OK (AMFI Metadata)</t>
+          <t>⚠️ MISSING - Map via App</t>
         </is>
       </c>
     </row>
@@ -10967,20 +10629,20 @@
         <v>30000</v>
       </c>
       <c r="I3" t="n">
-        <v>465.703</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>80131.19</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>167.1</v>
+        <v>-100</v>
       </c>
       <c r="L3" t="n">
-        <v>13.92</v>
+        <v>11.52</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>✅ OK (AMFI Metadata)</t>
+          <t>⚠️ MISSING - Map via App</t>
         </is>
       </c>
     </row>
@@ -11022,20 +10684,20 @@
         <v>41997.9</v>
       </c>
       <c r="I4" t="n">
-        <v>13.8506</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>60328.1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>43.65</v>
+        <v>-100</v>
       </c>
       <c r="L4" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>✅ OK (AMFI Metadata)</t>
+          <t>⚠️ MISSING - Map via App</t>
         </is>
       </c>
     </row>
@@ -11077,20 +10739,20 @@
         <v>39998</v>
       </c>
       <c r="I5" t="n">
-        <v>157.47</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>46872.52</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>17.19</v>
+        <v>-100</v>
       </c>
       <c r="L5" t="n">
-        <v>6.53</v>
+        <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>✅ OK (AMFI Metadata)</t>
+          <t>⚠️ MISSING - Map via App</t>
         </is>
       </c>
     </row>
@@ -11132,20 +10794,20 @@
         <v>41997.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5049.2657</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>50326.03</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>19.83</v>
+        <v>-100</v>
       </c>
       <c r="L6" t="n">
-        <v>11.84</v>
+        <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>✅ OK (AMFI Metadata)</t>
+          <t>⚠️ MISSING - Map via App</t>
         </is>
       </c>
     </row>
@@ -11187,20 +10849,20 @@
         <v>41997.9</v>
       </c>
       <c r="I7" t="n">
-        <v>46.2448</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>47189.12</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12.36</v>
+        <v>-100</v>
       </c>
       <c r="L7" t="n">
-        <v>7.35</v>
+        <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅ OK (AMFI Metadata)</t>
+          <t>⚠️ MISSING - Map via App</t>
         </is>
       </c>
     </row>
@@ -11242,20 +10904,20 @@
         <v>41997.9</v>
       </c>
       <c r="I8" t="n">
-        <v>17.157</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>48086.16</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>14.5</v>
+        <v>-100</v>
       </c>
       <c r="L8" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅ OK (AMFI Metadata)</t>
+          <t>⚠️ MISSING - Map via App</t>
         </is>
       </c>
     </row>
@@ -11297,20 +10959,20 @@
         <v>41997.9</v>
       </c>
       <c r="I9" t="n">
-        <v>171.599</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>44299.65</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5.48</v>
+        <v>-100</v>
       </c>
       <c r="L9" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅ OK (AMFI Metadata)</t>
+          <t>⚠️ MISSING - Map via App</t>
         </is>
       </c>
     </row>
@@ -11352,20 +11014,20 @@
         <v>5091.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1400.293</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>19877.16</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>290.39</v>
+        <v>-100</v>
       </c>
       <c r="L10" t="n">
-        <v>17.8</v>
+        <v>17.18</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>✅ OK (AMFI Metadata)</t>
+          <t>⚠️ MISSING - Map via App</t>
         </is>
       </c>
     </row>
@@ -11407,20 +11069,20 @@
         <v>41997.9</v>
       </c>
       <c r="I11" t="n">
-        <v>12.384</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>50442.29</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>20.11</v>
+        <v>-100</v>
       </c>
       <c r="L11" t="n">
-        <v>11.73</v>
+        <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>✅ OK (AMFI Metadata)</t>
+          <t>⚠️ MISSING - Map via App</t>
         </is>
       </c>
     </row>
@@ -11462,20 +11124,20 @@
         <v>41997.9</v>
       </c>
       <c r="I12" t="n">
-        <v>28.1984</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>49429.85</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>17.7</v>
+        <v>-100</v>
       </c>
       <c r="L12" t="n">
-        <v>10.26</v>
+        <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>✅ OK (AMFI Metadata)</t>
+          <t>⚠️ MISSING - Map via App</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11510,6 +11172,149 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Please add AMFI code</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Please add AMFI code</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Please add AMFI code</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Please add AMFI code</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Please add AMFI code</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Please add AMFI code</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Please add AMFI code</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Please add AMFI code</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Please add AMFI code</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Please add AMFI code</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Please add AMFI code</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
